--- a/INDEX.xlsx
+++ b/INDEX.xlsx
@@ -458,7 +458,7 @@
         <v>MONTHLY macd_line</v>
       </c>
       <c r="R1" t="str">
-        <v>MONTLY macd_signal</v>
+        <v>MONTHLY macd_signal</v>
       </c>
       <c r="S1" t="str">
         <v>Add Column</v>
@@ -502,7 +502,7 @@
         <v>12.36</v>
       </c>
       <c r="M2" s="3">
-        <v>-0.36</v>
+        <v>0.66</v>
       </c>
       <c r="N2" s="3">
         <v>0.65</v>
@@ -517,7 +517,7 @@
         <v>-0.09</v>
       </c>
       <c r="R2" s="3">
-        <v>0.65</v>
+        <v>0.02</v>
       </c>
       <c r="S2" t="str">
         <v/>
@@ -561,7 +561,7 @@
         <v>8374.79</v>
       </c>
       <c r="M3" s="3">
-        <v>-72.14</v>
+        <v>-56.26</v>
       </c>
       <c r="N3" s="3">
         <v>-87.73</v>
@@ -576,7 +576,7 @@
         <v>578.77</v>
       </c>
       <c r="R3" s="3">
-        <v>-87.73</v>
+        <v>686.08</v>
       </c>
       <c r="S3" t="str">
         <v/>
@@ -620,7 +620,7 @@
         <v>226.77</v>
       </c>
       <c r="M4" s="3">
-        <v>4.51</v>
+        <v>2.01</v>
       </c>
       <c r="N4" s="3">
         <v>2.91</v>
@@ -635,7 +635,7 @@
         <v>-0.82</v>
       </c>
       <c r="R4" s="3">
-        <v>2.91</v>
+        <v>-4.81</v>
       </c>
       <c r="S4" t="str">
         <v/>
@@ -679,7 +679,7 @@
         <v>183.97</v>
       </c>
       <c r="M5" s="3">
-        <v>3.35</v>
+        <v>1.61</v>
       </c>
       <c r="N5" s="3">
         <v>2.34</v>
@@ -694,7 +694,7 @@
         <v>-2.64</v>
       </c>
       <c r="R5" s="3">
-        <v>2.34</v>
+        <v>-6.06</v>
       </c>
       <c r="S5" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>3324.09</v>
       </c>
       <c r="M6" s="3">
-        <v>8.31</v>
+        <v>-11.82</v>
       </c>
       <c r="N6" s="3">
         <v>-10.63</v>
@@ -753,7 +753,7 @@
         <v>140.08</v>
       </c>
       <c r="R6" s="3">
-        <v>-10.63</v>
+        <v>155.52</v>
       </c>
       <c r="S6" t="str">
         <v/>
@@ -797,7 +797,7 @@
         <v>1609.47</v>
       </c>
       <c r="M7" s="3">
-        <v>7.04</v>
+        <v>-1.88</v>
       </c>
       <c r="N7" s="3">
         <v>-1.26</v>
@@ -812,7 +812,7 @@
         <v>35</v>
       </c>
       <c r="R7" s="3">
-        <v>-1.26</v>
+        <v>33.14</v>
       </c>
       <c r="S7" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1323.02</v>
       </c>
       <c r="M8" s="3">
-        <v>2.37</v>
+        <v>-3.88</v>
       </c>
       <c r="N8" s="3">
         <v>-3.27</v>
@@ -871,7 +871,7 @@
         <v>24.16</v>
       </c>
       <c r="R8" s="3">
-        <v>-3.27</v>
+        <v>24.25</v>
       </c>
       <c r="S8" t="str">
         <v/>
@@ -915,7 +915,7 @@
         <v>1459.16</v>
       </c>
       <c r="M9" s="3">
-        <v>4.37</v>
+        <v>-3.08</v>
       </c>
       <c r="N9" s="3">
         <v>-2.45</v>
@@ -930,7 +930,7 @@
         <v>29.31</v>
       </c>
       <c r="R9" s="3">
-        <v>-2.45</v>
+        <v>28.58</v>
       </c>
       <c r="S9" t="str">
         <v/>
@@ -974,7 +974,7 @@
         <v>1281.51</v>
       </c>
       <c r="M10" s="3">
-        <v>1.39</v>
+        <v>-4.53</v>
       </c>
       <c r="N10" s="3">
         <v>-3.79</v>
@@ -989,7 +989,7 @@
         <v>21.48</v>
       </c>
       <c r="R10" s="3">
-        <v>-3.79</v>
+        <v>21.99</v>
       </c>
       <c r="S10" t="str">
         <v/>
@@ -1033,7 +1033,7 @@
         <v>194.2</v>
       </c>
       <c r="M11" s="3">
-        <v>11.77</v>
+        <v>2.5</v>
       </c>
       <c r="N11" s="3">
         <v>2.54</v>
@@ -1048,7 +1048,7 @@
         <v>5.31</v>
       </c>
       <c r="R11" s="3">
-        <v>2.54</v>
+        <v>7.65</v>
       </c>
       <c r="S11" t="str">
         <v/>
@@ -1092,7 +1092,7 @@
         <v>3539.34</v>
       </c>
       <c r="M12" s="3">
-        <v>4.22</v>
+        <v>-16.47</v>
       </c>
       <c r="N12" s="3">
         <v>-14.31</v>
@@ -1107,7 +1107,7 @@
         <v>120.26</v>
       </c>
       <c r="R12" s="3">
-        <v>-14.31</v>
+        <v>142.19</v>
       </c>
       <c r="S12" t="str">
         <v/>
@@ -1124,19 +1124,19 @@
         <v>NIFTYGS813YR</v>
       </c>
       <c r="D13" s="1">
-        <v>2981.18</v>
+        <v>2980.67</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
       <c r="G13" s="2">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="H13" s="2">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -1145,28 +1145,28 @@
         <v>3001.37</v>
       </c>
       <c r="K13" s="1">
-        <v>2988.4</v>
+        <v>2988.3</v>
       </c>
       <c r="L13" s="1">
-        <v>3030.95</v>
+        <v>3030.94</v>
       </c>
       <c r="M13" s="3">
-        <v>1.17</v>
+        <v>-15.04</v>
       </c>
       <c r="N13" s="3">
         <v>-13.48</v>
       </c>
       <c r="O13" s="3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P13" s="3">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
       <c r="Q13" s="3">
-        <v>115.62</v>
+        <v>115.58</v>
       </c>
       <c r="R13" s="3">
-        <v>-13.48</v>
+        <v>132.99</v>
       </c>
       <c r="S13" t="str">
         <v/>
@@ -1183,19 +1183,19 @@
         <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D14" s="1">
-        <v>3073.57</v>
+        <v>3073.25</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="F14" s="2">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2">
-        <v>-0.99</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="2">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -1204,28 +1204,28 @@
         <v>3085.84</v>
       </c>
       <c r="K14" s="1">
-        <v>3080.32</v>
+        <v>3080.26</v>
       </c>
       <c r="L14" s="1">
-        <v>3122.97</v>
+        <v>3122.96</v>
       </c>
       <c r="M14" s="3">
-        <v>3.52</v>
+        <v>-14.85</v>
       </c>
       <c r="N14" s="3">
-        <v>-13.4</v>
+        <v>-13.41</v>
       </c>
       <c r="O14" s="3">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P14" s="3">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="Q14" s="3">
-        <v>119.52</v>
+        <v>119.5</v>
       </c>
       <c r="R14" s="3">
-        <v>-13.4</v>
+        <v>136.75</v>
       </c>
       <c r="S14" t="str">
         <v/>
@@ -1242,19 +1242,19 @@
         <v>NIFTYGS10YR</v>
       </c>
       <c r="D15" s="1">
-        <v>2608.99</v>
+        <v>2608.21</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="G15" s="2">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
       <c r="H15" s="2">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -1263,28 +1263,28 @@
         <v>2632.47</v>
       </c>
       <c r="K15" s="1">
-        <v>2615.26</v>
+        <v>2615.12</v>
       </c>
       <c r="L15" s="1">
-        <v>2653.16</v>
+        <v>2653.15</v>
       </c>
       <c r="M15" s="3">
-        <v>-1.16</v>
+        <v>-13.45</v>
       </c>
       <c r="N15" s="3">
-        <v>-12.07</v>
+        <v>-12.09</v>
       </c>
       <c r="O15" s="3">
-        <v>-1.16</v>
+        <v>-1.22</v>
       </c>
       <c r="P15" s="3">
-        <v>7.62</v>
+        <v>7.61</v>
       </c>
       <c r="Q15" s="3">
-        <v>90.65</v>
+        <v>90.59</v>
       </c>
       <c r="R15" s="3">
-        <v>-12.07</v>
+        <v>106.53</v>
       </c>
       <c r="S15" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v>10920.58</v>
       </c>
       <c r="M16" s="3">
-        <v>-217.36</v>
+        <v>-129.66</v>
       </c>
       <c r="N16" s="3">
         <v>-148.15</v>
@@ -1343,7 +1343,7 @@
         <v>81.1</v>
       </c>
       <c r="R16" s="3">
-        <v>-148.15</v>
+        <v>281.02</v>
       </c>
       <c r="S16" t="str">
         <v/>
@@ -1360,19 +1360,19 @@
         <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D17" s="1">
-        <v>842.29</v>
+        <v>842.03</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="H17" s="2">
-        <v>-5.51</v>
+        <v>-5.54</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -1381,28 +1381,28 @@
         <v>874.39</v>
       </c>
       <c r="K17" s="1">
-        <v>845.59</v>
+        <v>845.54</v>
       </c>
       <c r="L17" s="1">
-        <v>863.13</v>
+        <v>863.12</v>
       </c>
       <c r="M17" s="3">
-        <v>-8.43</v>
+        <v>-6.21</v>
       </c>
       <c r="N17" s="3">
         <v>-5.74</v>
       </c>
       <c r="O17" s="3">
-        <v>-8.43</v>
+        <v>-8.45</v>
       </c>
       <c r="P17" s="3">
         <v>-5.57</v>
       </c>
       <c r="Q17" s="3">
-        <v>-16.88</v>
+        <v>-16.9</v>
       </c>
       <c r="R17" s="3">
-        <v>-5.74</v>
+        <v>-14.13</v>
       </c>
       <c r="S17" t="str">
         <v/>
@@ -1446,7 +1446,7 @@
         <v>1572.07</v>
       </c>
       <c r="M18" s="3">
-        <v>37.41</v>
+        <v>21.7</v>
       </c>
       <c r="N18" s="3">
         <v>12.12</v>
@@ -1461,7 +1461,7 @@
         <v>-68.54</v>
       </c>
       <c r="R18" s="3">
-        <v>12.12</v>
+        <v>-104.6</v>
       </c>
       <c r="S18" t="str">
         <v/>
@@ -1505,7 +1505,7 @@
         <v>55763.52</v>
       </c>
       <c r="M19" s="3">
-        <v>790.27</v>
+        <v>-379.62</v>
       </c>
       <c r="N19" s="3">
         <v>-291.78</v>
@@ -1520,7 +1520,7 @@
         <v>3756.85</v>
       </c>
       <c r="R19" s="3">
-        <v>-291.78</v>
+        <v>3900.21</v>
       </c>
       <c r="S19" t="str">
         <v/>
@@ -1537,7 +1537,7 @@
         <v>NIFTYGS1115YR</v>
       </c>
       <c r="D20" s="1">
-        <v>3293.93</v>
+        <v>3294.03</v>
       </c>
       <c r="E20" s="2">
         <v>-0.28</v>
@@ -1549,7 +1549,7 @@
         <v>-0.83</v>
       </c>
       <c r="H20" s="2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -1558,13 +1558,13 @@
         <v>3294.67</v>
       </c>
       <c r="K20" s="1">
-        <v>3302.32</v>
+        <v>3302.34</v>
       </c>
       <c r="L20" s="1">
-        <v>3353.88</v>
+        <v>3353.89</v>
       </c>
       <c r="M20" s="3">
-        <v>8.25</v>
+        <v>-17.29</v>
       </c>
       <c r="N20" s="3">
         <v>-16.97</v>
@@ -1576,10 +1576,10 @@
         <v>21.63</v>
       </c>
       <c r="Q20" s="3">
-        <v>137.12</v>
+        <v>137.13</v>
       </c>
       <c r="R20" s="3">
-        <v>-16.97</v>
+        <v>154.03</v>
       </c>
       <c r="S20" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>54265.33</v>
       </c>
       <c r="M21" s="3">
-        <v>119.23</v>
+        <v>-513.88</v>
       </c>
       <c r="N21" s="3">
         <v>-448.09</v>
@@ -1638,7 +1638,7 @@
         <v>-663.92</v>
       </c>
       <c r="R21" s="3">
-        <v>-448.09</v>
+        <v>-1104.48</v>
       </c>
       <c r="S21" t="str">
         <v/>
@@ -1682,7 +1682,7 @@
         <v>71956.6</v>
       </c>
       <c r="M22" s="3">
-        <v>-115.29</v>
+        <v>-936.03</v>
       </c>
       <c r="N22" s="3">
         <v>-988.8</v>
@@ -1697,7 +1697,7 @@
         <v>2746.93</v>
       </c>
       <c r="R22" s="3">
-        <v>-988.8</v>
+        <v>3199.01</v>
       </c>
       <c r="S22" t="str">
         <v/>
@@ -1741,7 +1741,7 @@
         <v>12892.37</v>
       </c>
       <c r="M23" s="3">
-        <v>31.91</v>
+        <v>-269.43</v>
       </c>
       <c r="N23" s="3">
         <v>-239.21</v>
@@ -1756,7 +1756,7 @@
         <v>1154.3</v>
       </c>
       <c r="R23" s="3">
-        <v>-239.21</v>
+        <v>1133.55</v>
       </c>
       <c r="S23" t="str">
         <v/>
@@ -1800,7 +1800,7 @@
         <v>6324.49</v>
       </c>
       <c r="M24" s="3">
-        <v>-197.33</v>
+        <v>-92.33</v>
       </c>
       <c r="N24" s="3">
         <v>-91.23</v>
@@ -1815,7 +1815,7 @@
         <v>235.3</v>
       </c>
       <c r="R24" s="3">
-        <v>-91.23</v>
+        <v>404.21</v>
       </c>
       <c r="S24" t="str">
         <v/>
@@ -1859,7 +1859,7 @@
         <v>30395.42</v>
       </c>
       <c r="M25" s="3">
-        <v>-301.38</v>
+        <v>-375.34</v>
       </c>
       <c r="N25" s="3">
         <v>-355.55</v>
@@ -1874,7 +1874,7 @@
         <v>1491.04</v>
       </c>
       <c r="R25" s="3">
-        <v>-355.55</v>
+        <v>2007.93</v>
       </c>
       <c r="S25" t="str">
         <v/>
@@ -1918,7 +1918,7 @@
         <v>5706.91</v>
       </c>
       <c r="M26" s="3">
-        <v>-115.29</v>
+        <v>-39.72</v>
       </c>
       <c r="N26" s="3">
         <v>-71.03</v>
@@ -1933,7 +1933,7 @@
         <v>28.8</v>
       </c>
       <c r="R26" s="3">
-        <v>-71.03</v>
+        <v>140.24</v>
       </c>
       <c r="S26" t="str">
         <v/>
@@ -1977,7 +1977,7 @@
         <v>37551.17</v>
       </c>
       <c r="M27" s="3">
-        <v>-476.48</v>
+        <v>-461.17</v>
       </c>
       <c r="N27" s="3">
         <v>-471.75</v>
@@ -1992,7 +1992,7 @@
         <v>1005.91</v>
       </c>
       <c r="R27" s="3">
-        <v>-471.75</v>
+        <v>1242.5</v>
       </c>
       <c r="S27" t="str">
         <v/>
@@ -2036,7 +2036,7 @@
         <v>9837.16</v>
       </c>
       <c r="M28" s="3">
-        <v>219.67</v>
+        <v>-70.49</v>
       </c>
       <c r="N28" s="3">
         <v>-62.77</v>
@@ -2051,7 +2051,7 @@
         <v>750.26</v>
       </c>
       <c r="R28" s="3">
-        <v>-62.77</v>
+        <v>721.68</v>
       </c>
       <c r="S28" t="str">
         <v/>
@@ -2095,7 +2095,7 @@
         <v>9571.2</v>
       </c>
       <c r="M29" s="3">
-        <v>-220.01</v>
+        <v>-116.71</v>
       </c>
       <c r="N29" s="3">
         <v>-127.3</v>
@@ -2110,7 +2110,7 @@
         <v>800.38</v>
       </c>
       <c r="R29" s="3">
-        <v>-127.3</v>
+        <v>1093.5</v>
       </c>
       <c r="S29" t="str">
         <v/>
@@ -2154,7 +2154,7 @@
         <v>26266.15</v>
       </c>
       <c r="M30" s="3">
-        <v>-1.77</v>
+        <v>-308.66</v>
       </c>
       <c r="N30" s="3">
         <v>-307.25</v>
@@ -2169,7 +2169,7 @@
         <v>111.86</v>
       </c>
       <c r="R30" s="3">
-        <v>-307.25</v>
+        <v>-46.08</v>
       </c>
       <c r="S30" t="str">
         <v/>
@@ -2213,7 +2213,7 @@
         <v>15964.18</v>
       </c>
       <c r="M31" s="3">
-        <v>-74.41</v>
+        <v>-254.6</v>
       </c>
       <c r="N31" s="3">
         <v>-263.86</v>
@@ -2228,7 +2228,7 @@
         <v>1265.85</v>
       </c>
       <c r="R31" s="3">
-        <v>-263.86</v>
+        <v>1447.65</v>
       </c>
       <c r="S31" t="str">
         <v/>
@@ -2272,7 +2272,7 @@
         <v>56433.5</v>
       </c>
       <c r="M32" s="3">
-        <v>-306.23</v>
+        <v>-244.5</v>
       </c>
       <c r="N32" s="3">
         <v>-408.33</v>
@@ -2287,7 +2287,7 @@
         <v>1705.86</v>
       </c>
       <c r="R32" s="3">
-        <v>-408.33</v>
+        <v>2296.75</v>
       </c>
       <c r="S32" t="str">
         <v/>
@@ -2331,7 +2331,7 @@
         <v>26249.17</v>
       </c>
       <c r="M33" s="3">
-        <v>-331.06</v>
+        <v>-435.9</v>
       </c>
       <c r="N33" s="3">
         <v>-463.99</v>
@@ -2346,7 +2346,7 @@
         <v>1160.65</v>
       </c>
       <c r="R33" s="3">
-        <v>-463.99</v>
+        <v>1598.86</v>
       </c>
       <c r="S33" t="str">
         <v/>
@@ -2390,7 +2390,7 @@
         <v>26504.8</v>
       </c>
       <c r="M34" s="3">
-        <v>600.81</v>
+        <v>-232.47</v>
       </c>
       <c r="N34" s="3">
         <v>-146.16</v>
@@ -2405,7 +2405,7 @@
         <v>1776.15</v>
       </c>
       <c r="R34" s="3">
-        <v>-146.16</v>
+        <v>1607.67</v>
       </c>
       <c r="S34" t="str">
         <v/>
@@ -2449,7 +2449,7 @@
         <v>9541.65</v>
       </c>
       <c r="M35" s="3">
-        <v>-173.46</v>
+        <v>-162.81</v>
       </c>
       <c r="N35" s="3">
         <v>-170.28</v>
@@ -2464,7 +2464,7 @@
         <v>396.78</v>
       </c>
       <c r="R35" s="3">
-        <v>-170.28</v>
+        <v>509.72</v>
       </c>
       <c r="S35" t="str">
         <v/>
@@ -2508,7 +2508,7 @@
         <v>34069.02</v>
       </c>
       <c r="M36" s="3">
-        <v>-214.67</v>
+        <v>-413.87</v>
       </c>
       <c r="N36" s="3">
         <v>-478.8</v>
@@ -2523,7 +2523,7 @@
         <v>2028.91</v>
       </c>
       <c r="R36" s="3">
-        <v>-478.8</v>
+        <v>2435.7</v>
       </c>
       <c r="S36" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>9047.92</v>
       </c>
       <c r="M37" s="3">
-        <v>-158.3</v>
+        <v>-121.13</v>
       </c>
       <c r="N37" s="3">
         <v>-138.2</v>
@@ -2582,7 +2582,7 @@
         <v>272.98</v>
       </c>
       <c r="R37" s="3">
-        <v>-138.2</v>
+        <v>433.98</v>
       </c>
       <c r="S37" t="str">
         <v/>
@@ -2626,7 +2626,7 @@
         <v>27441.73</v>
       </c>
       <c r="M38" s="3">
-        <v>-250.8</v>
+        <v>-557.94</v>
       </c>
       <c r="N38" s="3">
         <v>-651.27</v>
@@ -2641,7 +2641,7 @@
         <v>1507.35</v>
       </c>
       <c r="R38" s="3">
-        <v>-651.27</v>
+        <v>1816.97</v>
       </c>
       <c r="S38" t="str">
         <v/>
@@ -2685,7 +2685,7 @@
         <v>48453.83</v>
       </c>
       <c r="M39" s="3">
-        <v>882.81</v>
+        <v>-244.43</v>
       </c>
       <c r="N39" s="3">
         <v>-212.11</v>
@@ -2700,7 +2700,7 @@
         <v>-226.03</v>
       </c>
       <c r="R39" s="3">
-        <v>-212.11</v>
+        <v>-997.05</v>
       </c>
       <c r="S39" t="str">
         <v/>
@@ -2744,7 +2744,7 @@
         <v>14196.36</v>
       </c>
       <c r="M40" s="3">
-        <v>-154.36</v>
+        <v>-193.83</v>
       </c>
       <c r="N40" s="3">
         <v>-207.46</v>
@@ -2759,7 +2759,7 @@
         <v>86.95</v>
       </c>
       <c r="R40" s="3">
-        <v>-207.46</v>
+        <v>120.57</v>
       </c>
       <c r="S40" t="str">
         <v/>
@@ -2803,7 +2803,7 @@
         <v>51027.93</v>
       </c>
       <c r="M41" s="3">
-        <v>190.45</v>
+        <v>-415.43</v>
       </c>
       <c r="N41" s="3">
         <v>-431.09</v>
@@ -2818,7 +2818,7 @@
         <v>135.15</v>
       </c>
       <c r="R41" s="3">
-        <v>-431.09</v>
+        <v>-284.13</v>
       </c>
       <c r="S41" t="str">
         <v/>
@@ -2862,7 +2862,7 @@
         <v>16493.32</v>
       </c>
       <c r="M42" s="3">
-        <v>-23.91</v>
+        <v>-233.31</v>
       </c>
       <c r="N42" s="3">
         <v>-241.96</v>
@@ -2877,7 +2877,7 @@
         <v>379.4</v>
       </c>
       <c r="R42" s="3">
-        <v>-241.96</v>
+        <v>332.77</v>
       </c>
       <c r="S42" t="str">
         <v/>
@@ -2921,7 +2921,7 @@
         <v>16397.36</v>
       </c>
       <c r="M43" s="3">
-        <v>174.74</v>
+        <v>-236.97</v>
       </c>
       <c r="N43" s="3">
         <v>-185.1</v>
@@ -2936,7 +2936,7 @@
         <v>982.44</v>
       </c>
       <c r="R43" s="3">
-        <v>-185.1</v>
+        <v>994.96</v>
       </c>
       <c r="S43" t="str">
         <v/>
@@ -2980,7 +2980,7 @@
         <v>62840.3</v>
       </c>
       <c r="M44" s="3">
-        <v>-272.63</v>
+        <v>-751.49</v>
       </c>
       <c r="N44" s="3">
         <v>-708.63</v>
@@ -2995,7 +2995,7 @@
         <v>-12.35</v>
       </c>
       <c r="R44" s="3">
-        <v>-708.63</v>
+        <v>-175.4</v>
       </c>
       <c r="S44" t="str">
         <v/>
@@ -3039,7 +3039,7 @@
         <v>5537.7</v>
       </c>
       <c r="M45" s="3">
-        <v>-40.87</v>
+        <v>-33.54</v>
       </c>
       <c r="N45" s="3">
         <v>-61.47</v>
@@ -3054,7 +3054,7 @@
         <v>192.26</v>
       </c>
       <c r="R45" s="3">
-        <v>-61.47</v>
+        <v>262.12</v>
       </c>
       <c r="S45" t="str">
         <v/>
@@ -3098,7 +3098,7 @@
         <v>51712.18</v>
       </c>
       <c r="M46" s="3">
-        <v>986.94</v>
+        <v>-742.76</v>
       </c>
       <c r="N46" s="3">
         <v>-535.44</v>
@@ -3113,7 +3113,7 @@
         <v>2197.92</v>
       </c>
       <c r="R46" s="3">
-        <v>-535.44</v>
+        <v>1477.16</v>
       </c>
       <c r="S46" t="str">
         <v/>
@@ -3157,7 +3157,7 @@
         <v>7797.25</v>
       </c>
       <c r="M47" s="3">
-        <v>-56.58</v>
+        <v>-85.41</v>
       </c>
       <c r="N47" s="3">
         <v>-86.41</v>
@@ -3172,7 +3172,7 @@
         <v>-294.39</v>
       </c>
       <c r="R47" s="3">
-        <v>-86.41</v>
+        <v>-246.06</v>
       </c>
       <c r="S47" t="str">
         <v/>
@@ -3216,7 +3216,7 @@
         <v>14077.98</v>
       </c>
       <c r="M48" s="3">
-        <v>-209.7</v>
+        <v>-87.76</v>
       </c>
       <c r="N48" s="3">
         <v>-177.27</v>
@@ -3231,7 +3231,7 @@
         <v>-529.62</v>
       </c>
       <c r="R48" s="3">
-        <v>-177.27</v>
+        <v>-490.47</v>
       </c>
       <c r="S48" t="str">
         <v/>
@@ -3275,7 +3275,7 @@
         <v>32105.82</v>
       </c>
       <c r="M49" s="3">
-        <v>-363.4</v>
+        <v>-349.66</v>
       </c>
       <c r="N49" s="3">
         <v>-440.21</v>
@@ -3290,7 +3290,7 @@
         <v>1850.76</v>
       </c>
       <c r="R49" s="3">
-        <v>-440.21</v>
+        <v>2377.64</v>
       </c>
       <c r="S49" t="str">
         <v/>
@@ -3334,7 +3334,7 @@
         <v>31753.46</v>
       </c>
       <c r="M50" s="3">
-        <v>-404.61</v>
+        <v>-646.57</v>
       </c>
       <c r="N50" s="3">
         <v>-629.11</v>
@@ -3349,7 +3349,7 @@
         <v>2038.85</v>
       </c>
       <c r="R50" s="3">
-        <v>-629.11</v>
+        <v>2407.67</v>
       </c>
       <c r="S50" t="str">
         <v/>
@@ -3393,7 +3393,7 @@
         <v>19583.61</v>
       </c>
       <c r="M51" s="3">
-        <v>-295.29</v>
+        <v>-232.6</v>
       </c>
       <c r="N51" s="3">
         <v>-284.84</v>
@@ -3408,7 +3408,7 @@
         <v>760.52</v>
       </c>
       <c r="R51" s="3">
-        <v>-284.84</v>
+        <v>1111.92</v>
       </c>
       <c r="S51" t="str">
         <v/>
@@ -3452,7 +3452,7 @@
         <v>9511</v>
       </c>
       <c r="M52" s="3">
-        <v>126.12</v>
+        <v>-89.98</v>
       </c>
       <c r="N52" s="3">
         <v>-101.8</v>
@@ -3467,7 +3467,7 @@
         <v>628</v>
       </c>
       <c r="R52" s="3">
-        <v>-101.8</v>
+        <v>527.7</v>
       </c>
       <c r="S52" t="str">
         <v/>
@@ -3511,7 +3511,7 @@
         <v>11122.31</v>
       </c>
       <c r="M53" s="3">
-        <v>-112.2</v>
+        <v>-79.61</v>
       </c>
       <c r="N53" s="3">
         <v>-160.82</v>
@@ -3526,7 +3526,7 @@
         <v>33.84</v>
       </c>
       <c r="R53" s="3">
-        <v>-160.82</v>
+        <v>177.01</v>
       </c>
       <c r="S53" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
         <v>24637.3</v>
       </c>
       <c r="M54" s="3">
-        <v>-327.95</v>
+        <v>-217.66</v>
       </c>
       <c r="N54" s="3">
         <v>-296.58</v>
@@ -3585,7 +3585,7 @@
         <v>344.58</v>
       </c>
       <c r="R54" s="3">
-        <v>-296.58</v>
+        <v>711.08</v>
       </c>
       <c r="S54" t="str">
         <v/>
@@ -3629,7 +3629,7 @@
         <v>5309.82</v>
       </c>
       <c r="M55" s="3">
-        <v>38.14</v>
+        <v>-20.36</v>
       </c>
       <c r="N55" s="3">
         <v>-30.17</v>
@@ -3644,7 +3644,7 @@
         <v>374.58</v>
       </c>
       <c r="R55" s="3">
-        <v>-30.17</v>
+        <v>327.38</v>
       </c>
       <c r="S55" t="str">
         <v/>
@@ -3688,7 +3688,7 @@
         <v>19680.38</v>
       </c>
       <c r="M56" s="3">
-        <v>339.32</v>
+        <v>-154.16</v>
       </c>
       <c r="N56" s="3">
         <v>-129.79</v>
@@ -3703,7 +3703,7 @@
         <v>892.77</v>
       </c>
       <c r="R56" s="3">
-        <v>-129.79</v>
+        <v>862.73</v>
       </c>
       <c r="S56" t="str">
         <v/>
@@ -3747,7 +3747,7 @@
         <v>13681.72</v>
       </c>
       <c r="M57" s="3">
-        <v>-155.64</v>
+        <v>-134.36</v>
       </c>
       <c r="N57" s="3">
         <v>-171.64</v>
@@ -3762,7 +3762,7 @@
         <v>280.21</v>
       </c>
       <c r="R57" s="3">
-        <v>-171.64</v>
+        <v>466.43</v>
       </c>
       <c r="S57" t="str">
         <v/>
@@ -3806,7 +3806,7 @@
         <v>22869.12</v>
       </c>
       <c r="M58" s="3">
-        <v>-192.69</v>
+        <v>-225.46</v>
       </c>
       <c r="N58" s="3">
         <v>-275.42</v>
@@ -3821,7 +3821,7 @@
         <v>533.73</v>
       </c>
       <c r="R58" s="3">
-        <v>-275.42</v>
+        <v>808.69</v>
       </c>
       <c r="S58" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>16366.58</v>
       </c>
       <c r="M59" s="3">
-        <v>-133.4</v>
+        <v>-185.36</v>
       </c>
       <c r="N59" s="3">
         <v>-216.84</v>
@@ -3880,7 +3880,7 @@
         <v>929.32</v>
       </c>
       <c r="R59" s="3">
-        <v>-216.84</v>
+        <v>1181.35</v>
       </c>
       <c r="S59" t="str">
         <v/>
@@ -3924,7 +3924,7 @@
         <v>17751.15</v>
       </c>
       <c r="M60" s="3">
-        <v>-33.85</v>
+        <v>-261.77</v>
       </c>
       <c r="N60" s="3">
         <v>-278.24</v>
@@ -3939,7 +3939,7 @@
         <v>915.94</v>
       </c>
       <c r="R60" s="3">
-        <v>-278.24</v>
+        <v>1051.43</v>
       </c>
       <c r="S60" t="str">
         <v/>
@@ -3983,7 +3983,7 @@
         <v>16277.41</v>
       </c>
       <c r="M61" s="3">
-        <v>-59.62</v>
+        <v>-162.34</v>
       </c>
       <c r="N61" s="3">
         <v>-186.97</v>
@@ -3998,7 +3998,7 @@
         <v>933.56</v>
       </c>
       <c r="R61" s="3">
-        <v>-186.97</v>
+        <v>1151.4</v>
       </c>
       <c r="S61" t="str">
         <v/>
@@ -4042,7 +4042,7 @@
         <v>12934.02</v>
       </c>
       <c r="M62" s="3">
-        <v>-86.46</v>
+        <v>-125.26</v>
       </c>
       <c r="N62" s="3">
         <v>-150.83</v>
@@ -4057,7 +4057,7 @@
         <v>640.24</v>
       </c>
       <c r="R62" s="3">
-        <v>-150.83</v>
+        <v>828.13</v>
       </c>
       <c r="S62" t="str">
         <v/>
@@ -4101,7 +4101,7 @@
         <v>11533.73</v>
       </c>
       <c r="M63" s="3">
-        <v>-142.76</v>
+        <v>-165.76</v>
       </c>
       <c r="N63" s="3">
         <v>-187.83</v>
@@ -4116,7 +4116,7 @@
         <v>225.56</v>
       </c>
       <c r="R63" s="3">
-        <v>-187.83</v>
+        <v>395.78</v>
       </c>
       <c r="S63" t="str">
         <v/>
@@ -4160,7 +4160,7 @@
         <v>61831.43</v>
       </c>
       <c r="M64" s="3">
-        <v>-224.86</v>
+        <v>-847.38</v>
       </c>
       <c r="N64" s="3">
         <v>-899.29</v>
@@ -4175,7 +4175,7 @@
         <v>2942.36</v>
       </c>
       <c r="R64" s="3">
-        <v>-899.29</v>
+        <v>3494.39</v>
       </c>
       <c r="S64" t="str">
         <v/>
@@ -4219,7 +4219,7 @@
         <v>22724.19</v>
       </c>
       <c r="M65" s="3">
-        <v>-80.46</v>
+        <v>-313.55</v>
       </c>
       <c r="N65" s="3">
         <v>-328.14</v>
@@ -4234,7 +4234,7 @@
         <v>1726.57</v>
       </c>
       <c r="R65" s="3">
-        <v>-328.14</v>
+        <v>2031.93</v>
       </c>
       <c r="S65" t="str">
         <v/>
@@ -4278,7 +4278,7 @@
         <v>4884.75</v>
       </c>
       <c r="M66" s="3">
-        <v>-47.12</v>
+        <v>-43.77</v>
       </c>
       <c r="N66" s="3">
         <v>-63.54</v>
@@ -4293,7 +4293,7 @@
         <v>223.49</v>
       </c>
       <c r="R66" s="3">
-        <v>-63.54</v>
+        <v>300.13</v>
       </c>
       <c r="S66" t="str">
         <v/>
@@ -4337,7 +4337,7 @@
         <v>23514.27</v>
       </c>
       <c r="M67" s="3">
-        <v>-378</v>
+        <v>-185.04</v>
       </c>
       <c r="N67" s="3">
         <v>-273.79</v>
@@ -4352,7 +4352,7 @@
         <v>200.23</v>
       </c>
       <c r="R67" s="3">
-        <v>-273.79</v>
+        <v>600.9</v>
       </c>
       <c r="S67" t="str">
         <v/>
@@ -4396,7 +4396,7 @@
         <v>21071.25</v>
       </c>
       <c r="M68" s="3">
-        <v>46.95</v>
+        <v>-252.22</v>
       </c>
       <c r="N68" s="3">
         <v>-253.81</v>
@@ -4411,7 +4411,7 @@
         <v>1600.32</v>
       </c>
       <c r="R68" s="3">
-        <v>-253.81</v>
+        <v>1827.81</v>
       </c>
       <c r="S68" t="str">
         <v/>
@@ -4455,7 +4455,7 @@
         <v>14407.94</v>
       </c>
       <c r="M69" s="3">
-        <v>-53.14</v>
+        <v>-218.84</v>
       </c>
       <c r="N69" s="3">
         <v>-240.63</v>
@@ -4470,7 +4470,7 @@
         <v>887.23</v>
       </c>
       <c r="R69" s="3">
-        <v>-240.63</v>
+        <v>1004.13</v>
       </c>
       <c r="S69" t="str">
         <v/>
@@ -4514,7 +4514,7 @@
         <v>38605.84</v>
       </c>
       <c r="M70" s="3">
-        <v>-143</v>
+        <v>-700.92</v>
       </c>
       <c r="N70" s="3">
         <v>-737.05</v>
@@ -4529,7 +4529,7 @@
         <v>685.97</v>
       </c>
       <c r="R70" s="3">
-        <v>-737.05</v>
+        <v>949.36</v>
       </c>
       <c r="S70" t="str">
         <v/>
@@ -4573,7 +4573,7 @@
         <v>18138.87</v>
       </c>
       <c r="M71" s="3">
-        <v>238.04</v>
+        <v>-154.43</v>
       </c>
       <c r="N71" s="3">
         <v>-136.52</v>
@@ -4588,7 +4588,7 @@
         <v>1339.23</v>
       </c>
       <c r="R71" s="3">
-        <v>-136.52</v>
+        <v>1435.09</v>
       </c>
       <c r="S71" t="str">
         <v/>
@@ -4632,7 +4632,7 @@
         <v>7418.47</v>
       </c>
       <c r="M72" s="3">
-        <v>2.99</v>
+        <v>-14.64</v>
       </c>
       <c r="N72" s="3">
         <v>-58.79</v>
@@ -4647,7 +4647,7 @@
         <v>473.87</v>
       </c>
       <c r="R72" s="3">
-        <v>-58.79</v>
+        <v>552.98</v>
       </c>
       <c r="S72" t="str">
         <v/>
@@ -4691,7 +4691,7 @@
         <v>23833.06</v>
       </c>
       <c r="M73" s="3">
-        <v>-179.1</v>
+        <v>-257.13</v>
       </c>
       <c r="N73" s="3">
         <v>-301.12</v>
@@ -4706,7 +4706,7 @@
         <v>1041.01</v>
       </c>
       <c r="R73" s="3">
-        <v>-301.12</v>
+        <v>1363.04</v>
       </c>
       <c r="S73" t="str">
         <v/>
@@ -4750,7 +4750,7 @@
         <v>19894.51</v>
       </c>
       <c r="M74" s="3">
-        <v>-258.22</v>
+        <v>-157.5</v>
       </c>
       <c r="N74" s="3">
         <v>-252.48</v>
@@ -4765,7 +4765,7 @@
         <v>507.8</v>
       </c>
       <c r="R74" s="3">
-        <v>-252.48</v>
+        <v>799.61</v>
       </c>
       <c r="S74" t="str">
         <v/>
@@ -4809,7 +4809,7 @@
         <v>867.25</v>
       </c>
       <c r="M75" s="3">
-        <v>0.89</v>
+        <v>-13.57</v>
       </c>
       <c r="N75" s="3">
         <v>-14.54</v>
@@ -4824,7 +4824,7 @@
         <v>2.54</v>
       </c>
       <c r="R75" s="3">
-        <v>-14.54</v>
+        <v>10.09</v>
       </c>
       <c r="S75" t="str">
         <v/>
@@ -4868,7 +4868,7 @@
         <v>11584.13</v>
       </c>
       <c r="M76" s="3">
-        <v>-258.76</v>
+        <v>-59.98</v>
       </c>
       <c r="N76" s="3">
         <v>-115.63</v>
@@ -4883,7 +4883,7 @@
         <v>-124.74</v>
       </c>
       <c r="R76" s="3">
-        <v>-115.63</v>
+        <v>115.49</v>
       </c>
       <c r="S76" t="str">
         <v/>
@@ -4927,7 +4927,7 @@
         <v>30157.43</v>
       </c>
       <c r="M77" s="3">
-        <v>-346.4</v>
+        <v>-65.9</v>
       </c>
       <c r="N77" s="3">
         <v>-249.18</v>
@@ -4942,7 +4942,7 @@
         <v>495.29</v>
       </c>
       <c r="R77" s="3">
-        <v>-249.18</v>
+        <v>993.55</v>
       </c>
       <c r="S77" t="str">
         <v/>
@@ -4986,7 +4986,7 @@
         <v>16888.42</v>
       </c>
       <c r="M78" s="3">
-        <v>43.53</v>
+        <v>-238.03</v>
       </c>
       <c r="N78" s="3">
         <v>-235.4</v>
@@ -5001,7 +5001,7 @@
         <v>1565.9</v>
       </c>
       <c r="R78" s="3">
-        <v>-235.4</v>
+        <v>1751.51</v>
       </c>
       <c r="S78" t="str">
         <v/>
@@ -5045,7 +5045,7 @@
         <v>29809.61</v>
       </c>
       <c r="M79" s="3">
-        <v>-195.07</v>
+        <v>395.38</v>
       </c>
       <c r="N79" s="3">
         <v>-87.44</v>
@@ -5060,7 +5060,7 @@
         <v>-1699.24</v>
       </c>
       <c r="R79" s="3">
-        <v>-87.44</v>
+        <v>-1155.4</v>
       </c>
       <c r="S79" t="str">
         <v/>
@@ -5104,7 +5104,7 @@
         <v>8415.39</v>
       </c>
       <c r="M80" s="3">
-        <v>-157.19</v>
+        <v>-20.17</v>
       </c>
       <c r="N80" s="3">
         <v>-63.71</v>
@@ -5119,7 +5119,7 @@
         <v>-302.52</v>
       </c>
       <c r="R80" s="3">
-        <v>-63.71</v>
+        <v>-191.83</v>
       </c>
       <c r="S80" t="str">
         <v/>
@@ -5163,7 +5163,7 @@
         <v>8541.32</v>
       </c>
       <c r="M81" s="3">
-        <v>68.86</v>
+        <v>-4.23</v>
       </c>
       <c r="N81" s="3">
         <v>-71.71</v>
@@ -5178,7 +5178,7 @@
         <v>375.34</v>
       </c>
       <c r="R81" s="3">
-        <v>-71.71</v>
+        <v>514.31</v>
       </c>
       <c r="S81" t="str">
         <v/>
@@ -5222,7 +5222,7 @@
         <v>3939.04</v>
       </c>
       <c r="M82" s="3">
-        <v>-64.32</v>
+        <v>-36.3</v>
       </c>
       <c r="N82" s="3">
         <v>-50.99</v>
@@ -5237,7 +5237,7 @@
         <v>127.86</v>
       </c>
       <c r="R82" s="3">
-        <v>-50.99</v>
+        <v>207.1</v>
       </c>
       <c r="S82" t="str">
         <v/>
@@ -5281,7 +5281,7 @@
         <v>27702.92</v>
       </c>
       <c r="M83" s="3">
-        <v>-456.58</v>
+        <v>-198.76</v>
       </c>
       <c r="N83" s="3">
         <v>-288.55</v>
@@ -5296,7 +5296,7 @@
         <v>1333.07</v>
       </c>
       <c r="R83" s="3">
-        <v>-288.55</v>
+        <v>1904.53</v>
       </c>
       <c r="S83" t="str">
         <v/>
@@ -5340,7 +5340,7 @@
         <v>46121.99</v>
       </c>
       <c r="M84" s="3">
-        <v>-1598.77</v>
+        <v>-456.81</v>
       </c>
       <c r="N84" s="3">
         <v>-504.62</v>
@@ -5355,7 +5355,7 @@
         <v>-2116.54</v>
       </c>
       <c r="R84" s="3">
-        <v>-504.62</v>
+        <v>-956.12</v>
       </c>
       <c r="S84" t="str">
         <v/>
@@ -5399,7 +5399,7 @@
         <v>25597.84</v>
       </c>
       <c r="M85" s="3">
-        <v>-331.83</v>
+        <v>-121.71</v>
       </c>
       <c r="N85" s="3">
         <v>-206.59</v>
@@ -5414,7 +5414,7 @@
         <v>674.52</v>
       </c>
       <c r="R85" s="3">
-        <v>-206.59</v>
+        <v>1086.46</v>
       </c>
       <c r="S85" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
         <v>29468.3</v>
       </c>
       <c r="M86" s="3">
-        <v>-130.04</v>
+        <v>-354.18</v>
       </c>
       <c r="N86" s="3">
         <v>-394.92</v>
@@ -5473,7 +5473,7 @@
         <v>282.81</v>
       </c>
       <c r="R86" s="3">
-        <v>-394.92</v>
+        <v>197.84</v>
       </c>
       <c r="S86" t="str">
         <v/>
@@ -5517,7 +5517,7 @@
         <v>26179.41</v>
       </c>
       <c r="M87" s="3">
-        <v>683.83</v>
+        <v>-172.58</v>
       </c>
       <c r="N87" s="3">
         <v>-106.49</v>
@@ -5532,7 +5532,7 @@
         <v>2363.37</v>
       </c>
       <c r="R87" s="3">
-        <v>-106.49</v>
+        <v>2365.37</v>
       </c>
       <c r="S87" t="str">
         <v/>
@@ -5576,7 +5576,7 @@
         <v>27306.52</v>
       </c>
       <c r="M88" s="3">
-        <v>-11.17</v>
+        <v>29.87</v>
       </c>
       <c r="N88" s="3">
         <v>-52.8</v>
@@ -5591,7 +5591,7 @@
         <v>672.45</v>
       </c>
       <c r="R88" s="3">
-        <v>-52.8</v>
+        <v>880.38</v>
       </c>
       <c r="S88" t="str">
         <v/>
@@ -5635,7 +5635,7 @@
         <v>17256.4</v>
       </c>
       <c r="M89" s="3">
-        <v>-658.68</v>
+        <v>-299.59</v>
       </c>
       <c r="N89" s="3">
         <v>-425.54</v>
@@ -5650,7 +5650,7 @@
         <v>280.73</v>
       </c>
       <c r="R89" s="3">
-        <v>-425.54</v>
+        <v>929.94</v>
       </c>
       <c r="S89" t="str">
         <v/>
@@ -5694,7 +5694,7 @@
         <v>11321.07</v>
       </c>
       <c r="M90" s="3">
-        <v>-477.57</v>
+        <v>-198.96</v>
       </c>
       <c r="N90" s="3">
         <v>-281.64</v>
@@ -5709,7 +5709,7 @@
         <v>-3.9</v>
       </c>
       <c r="R90" s="3">
-        <v>-281.64</v>
+        <v>426.64</v>
       </c>
       <c r="S90" t="str">
         <v/>

--- a/INDEX.xlsx
+++ b/INDEX.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:Y90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,6 +461,24 @@
         <v>MONTHLY macd_signal</v>
       </c>
       <c r="S1" t="str">
+        <v>rsi</v>
+      </c>
+      <c r="T1" t="str">
+        <v>adx_di_positive</v>
+      </c>
+      <c r="U1" t="str">
+        <v>adx_di_negative</v>
+      </c>
+      <c r="V1" t="str">
+        <v>adx</v>
+      </c>
+      <c r="W1" t="str">
+        <v>market_cap</v>
+      </c>
+      <c r="X1" t="str">
+        <v>earning_per_share</v>
+      </c>
+      <c r="Y1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -469,57 +487,75 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>India VIX</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C2" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D2" s="1">
-        <v>14.77</v>
+        <v>51181.5</v>
       </c>
       <c r="E2" s="2">
-        <v>5.05</v>
+        <v>2.55</v>
       </c>
       <c r="F2" s="2">
-        <v>5.05</v>
+        <v>2.55</v>
       </c>
       <c r="G2" s="2">
-        <v>9.49</v>
+        <v>-5.36</v>
       </c>
       <c r="H2" s="2">
-        <v>55.8</v>
+        <v>1.73</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>14.81</v>
+        <v>52200.26</v>
       </c>
       <c r="K2" s="1">
-        <v>14.27</v>
+        <v>52616.29</v>
       </c>
       <c r="L2" s="1">
-        <v>12.36</v>
+        <v>55348.14</v>
       </c>
       <c r="M2" s="3">
-        <v>0.66</v>
+        <v>-1058.59</v>
       </c>
       <c r="N2" s="3">
-        <v>0.65</v>
+        <v>-631.28</v>
       </c>
       <c r="O2" s="3">
-        <v>-0.36</v>
+        <v>213.47</v>
       </c>
       <c r="P2" s="3">
-        <v>-0.76</v>
+        <v>932.69</v>
       </c>
       <c r="Q2" s="3">
-        <v>-0.09</v>
+        <v>3555.95</v>
       </c>
       <c r="R2" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="S2" t="str">
+        <v>3860.03</v>
+      </c>
+      <c r="S2" s="3">
+        <v>34.48</v>
+      </c>
+      <c r="T2" s="3">
+        <v>8.55</v>
+      </c>
+      <c r="U2" s="3">
+        <v>45.64</v>
+      </c>
+      <c r="V2" s="3">
+        <v>36.07</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="str">
         <v/>
       </c>
     </row>
@@ -528,57 +564,75 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D3" s="1">
-        <v>8294.1</v>
+        <v>50221.55</v>
       </c>
       <c r="E3" s="2">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="F3" s="2">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="G3" s="2">
-        <v>3.47</v>
+        <v>-5.05</v>
       </c>
       <c r="H3" s="2">
-        <v>-2.8</v>
+        <v>-4.72</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>8575.33</v>
+        <v>52510.51</v>
       </c>
       <c r="K3" s="1">
-        <v>8128.49</v>
+        <v>51253.27</v>
       </c>
       <c r="L3" s="1">
-        <v>8374.79</v>
+        <v>53875.24</v>
       </c>
       <c r="M3" s="3">
-        <v>-56.26</v>
+        <v>-996.06</v>
       </c>
       <c r="N3" s="3">
-        <v>-87.73</v>
+        <v>-695.74</v>
       </c>
       <c r="O3" s="3">
-        <v>-72.14</v>
+        <v>-330.62</v>
       </c>
       <c r="P3" s="3">
-        <v>-29.08</v>
+        <v>264.31</v>
       </c>
       <c r="Q3" s="3">
-        <v>578.77</v>
+        <v>-818.06</v>
       </c>
       <c r="R3" s="3">
-        <v>686.08</v>
-      </c>
-      <c r="S3" t="str">
+        <v>-1135.31</v>
+      </c>
+      <c r="S3" s="3">
+        <v>34.88</v>
+      </c>
+      <c r="T3" s="3">
+        <v>6.91</v>
+      </c>
+      <c r="U3" s="3">
+        <v>44.85</v>
+      </c>
+      <c r="V3" s="3">
+        <v>42.94</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="str">
         <v/>
       </c>
     </row>
@@ -587,57 +641,75 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D4" s="1">
-        <v>233.5</v>
+        <v>7529.45</v>
       </c>
       <c r="E4" s="2">
-        <v>1.15</v>
+        <v>2.35</v>
       </c>
       <c r="F4" s="2">
-        <v>1.15</v>
+        <v>2.35</v>
       </c>
       <c r="G4" s="2">
-        <v>-1.04</v>
+        <v>-2.27</v>
       </c>
       <c r="H4" s="2">
-        <v>16.75</v>
+        <v>-12.49</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>218.74</v>
+        <v>7674.26</v>
       </c>
       <c r="K4" s="1">
-        <v>234.35</v>
+        <v>7479.91</v>
       </c>
       <c r="L4" s="1">
-        <v>226.77</v>
+        <v>7741.94</v>
       </c>
       <c r="M4" s="3">
-        <v>2.01</v>
+        <v>-85.83</v>
       </c>
       <c r="N4" s="3">
-        <v>2.91</v>
+        <v>-89.2</v>
       </c>
       <c r="O4" s="3">
-        <v>4.51</v>
+        <v>-74.02</v>
       </c>
       <c r="P4" s="3">
-        <v>3.42</v>
+        <v>-29.88</v>
       </c>
       <c r="Q4" s="3">
-        <v>-0.82</v>
+        <v>-291.89</v>
       </c>
       <c r="R4" s="3">
-        <v>-4.81</v>
-      </c>
-      <c r="S4" t="str">
+        <v>-245.56</v>
+      </c>
+      <c r="S4" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="T4" s="3">
+        <v>16.13</v>
+      </c>
+      <c r="U4" s="3">
+        <v>26.17</v>
+      </c>
+      <c r="V4" s="3">
+        <v>25.98</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="str">
         <v/>
       </c>
     </row>
@@ -646,57 +718,75 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D5" s="1">
-        <v>189.35</v>
+        <v>11731.55</v>
       </c>
       <c r="E5" s="2">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="F5" s="2">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="G5" s="2">
-        <v>-1.07</v>
+        <v>-8.06</v>
       </c>
       <c r="H5" s="2">
-        <v>15.7</v>
+        <v>5.05</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>178.28</v>
+        <v>12486.09</v>
       </c>
       <c r="K5" s="1">
-        <v>190.07</v>
+        <v>11911.42</v>
       </c>
       <c r="L5" s="1">
-        <v>183.97</v>
+        <v>12775.95</v>
       </c>
       <c r="M5" s="3">
-        <v>1.61</v>
+        <v>-314.44</v>
       </c>
       <c r="N5" s="3">
-        <v>2.34</v>
+        <v>-276.53</v>
       </c>
       <c r="O5" s="3">
-        <v>3.35</v>
+        <v>-75.27</v>
       </c>
       <c r="P5" s="3">
-        <v>2.45</v>
+        <v>147.26</v>
       </c>
       <c r="Q5" s="3">
-        <v>-2.64</v>
+        <v>1127.59</v>
       </c>
       <c r="R5" s="3">
-        <v>-6.06</v>
-      </c>
-      <c r="S5" t="str">
+        <v>1128.21</v>
+      </c>
+      <c r="S5" s="3">
+        <v>36.15</v>
+      </c>
+      <c r="T5" s="3">
+        <v>10.25</v>
+      </c>
+      <c r="U5" s="3">
+        <v>36.88</v>
+      </c>
+      <c r="V5" s="3">
+        <v>36.83</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="str">
         <v/>
       </c>
     </row>
@@ -705,57 +795,75 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D6" s="1">
-        <v>3284.34</v>
+        <v>48694</v>
       </c>
       <c r="E6" s="2">
-        <v>0.09</v>
+        <v>2.19</v>
       </c>
       <c r="F6" s="2">
-        <v>0.09</v>
+        <v>2.19</v>
       </c>
       <c r="G6" s="2">
-        <v>-0.73</v>
+        <v>-4.49</v>
       </c>
       <c r="H6" s="2">
-        <v>1.91</v>
+        <v>11.01</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>3279.61</v>
+        <v>47382.23</v>
       </c>
       <c r="K6" s="1">
-        <v>3289.81</v>
+        <v>48986.82</v>
       </c>
       <c r="L6" s="1">
-        <v>3324.09</v>
+        <v>51371.99</v>
       </c>
       <c r="M6" s="3">
-        <v>-11.82</v>
+        <v>-944.01</v>
       </c>
       <c r="N6" s="3">
-        <v>-10.63</v>
+        <v>-760.44</v>
       </c>
       <c r="O6" s="3">
-        <v>8.31</v>
+        <v>684.38</v>
       </c>
       <c r="P6" s="3">
-        <v>18.11</v>
+        <v>1377.64</v>
       </c>
       <c r="Q6" s="3">
-        <v>140.08</v>
+        <v>2184.16</v>
       </c>
       <c r="R6" s="3">
-        <v>155.52</v>
-      </c>
-      <c r="S6" t="str">
+        <v>1474.4</v>
+      </c>
+      <c r="S6" s="3">
+        <v>36.98</v>
+      </c>
+      <c r="T6" s="3">
+        <v>10.23</v>
+      </c>
+      <c r="U6" s="3">
+        <v>34.79</v>
+      </c>
+      <c r="V6" s="3">
+        <v>40.92</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="str">
         <v/>
       </c>
     </row>
@@ -764,57 +872,75 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C7" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D7" s="1">
-        <v>1602.59</v>
+        <v>27862.75</v>
       </c>
       <c r="E7" s="2">
-        <v>0.07</v>
+        <v>2.05</v>
       </c>
       <c r="F7" s="2">
-        <v>0.07</v>
+        <v>2.05</v>
       </c>
       <c r="G7" s="2">
-        <v>-0.27</v>
+        <v>-5.61</v>
       </c>
       <c r="H7" s="2">
-        <v>2.28</v>
+        <v>-10.55</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>1586.32</v>
+        <v>30349.35</v>
       </c>
       <c r="K7" s="1">
-        <v>1604.46</v>
+        <v>28456.84</v>
       </c>
       <c r="L7" s="1">
-        <v>1609.47</v>
+        <v>30123.15</v>
       </c>
       <c r="M7" s="3">
-        <v>-1.88</v>
+        <v>-616.75</v>
       </c>
       <c r="N7" s="3">
-        <v>-1.26</v>
+        <v>-471.96</v>
       </c>
       <c r="O7" s="3">
-        <v>7.04</v>
+        <v>-540.32</v>
       </c>
       <c r="P7" s="3">
-        <v>9.39</v>
+        <v>-191.77</v>
       </c>
       <c r="Q7" s="3">
-        <v>35</v>
+        <v>1406.3</v>
       </c>
       <c r="R7" s="3">
-        <v>33.14</v>
-      </c>
-      <c r="S7" t="str">
+        <v>1990.98</v>
+      </c>
+      <c r="S7" s="3">
+        <v>33.05</v>
+      </c>
+      <c r="T7" s="3">
+        <v>6.94</v>
+      </c>
+      <c r="U7" s="3">
+        <v>41.84</v>
+      </c>
+      <c r="V7" s="3">
+        <v>42.88</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="str">
         <v/>
       </c>
     </row>
@@ -823,57 +949,75 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C8" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D8" s="1">
-        <v>1308.53</v>
+        <v>57955.6</v>
       </c>
       <c r="E8" s="2">
-        <v>0.06</v>
+        <v>2.01</v>
       </c>
       <c r="F8" s="2">
-        <v>0.06</v>
+        <v>2.01</v>
       </c>
       <c r="G8" s="2">
-        <v>-0.53</v>
+        <v>-4.64</v>
       </c>
       <c r="H8" s="2">
-        <v>0.8</v>
+        <v>-6.4</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>1307.91</v>
+        <v>61681.34</v>
       </c>
       <c r="K8" s="1">
-        <v>1311.79</v>
+        <v>59024.73</v>
       </c>
       <c r="L8" s="1">
-        <v>1323.02</v>
+        <v>62328.51</v>
       </c>
       <c r="M8" s="3">
-        <v>-3.88</v>
+        <v>-1210.4</v>
       </c>
       <c r="N8" s="3">
-        <v>-3.27</v>
+        <v>-935.87</v>
       </c>
       <c r="O8" s="3">
-        <v>2.37</v>
+        <v>-736.86</v>
       </c>
       <c r="P8" s="3">
-        <v>5.74</v>
+        <v>3.56</v>
       </c>
       <c r="Q8" s="3">
-        <v>24.16</v>
+        <v>-157.46</v>
       </c>
       <c r="R8" s="3">
-        <v>24.25</v>
-      </c>
-      <c r="S8" t="str">
+        <v>-204.43</v>
+      </c>
+      <c r="S8" s="3">
+        <v>33.3</v>
+      </c>
+      <c r="T8" s="3">
+        <v>6.88</v>
+      </c>
+      <c r="U8" s="3">
+        <v>42.24</v>
+      </c>
+      <c r="V8" s="3">
+        <v>45.58</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="str">
         <v/>
       </c>
     </row>
@@ -882,57 +1026,75 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C9" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D9" s="1">
-        <v>1447.65</v>
+        <v>5018.6</v>
       </c>
       <c r="E9" s="2">
-        <v>0.04</v>
+        <v>1.8</v>
       </c>
       <c r="F9" s="2">
-        <v>0.04</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="2">
-        <v>-0.43</v>
+        <v>-1.4</v>
       </c>
       <c r="H9" s="2">
-        <v>1.61</v>
+        <v>7.78</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>1440.58</v>
+        <v>5108.62</v>
       </c>
       <c r="K9" s="1">
-        <v>1450.48</v>
+        <v>5109.83</v>
       </c>
       <c r="L9" s="1">
-        <v>1459.16</v>
+        <v>5287.83</v>
       </c>
       <c r="M9" s="3">
-        <v>-3.08</v>
+        <v>-63.71</v>
       </c>
       <c r="N9" s="3">
-        <v>-2.45</v>
+        <v>-42.84</v>
       </c>
       <c r="O9" s="3">
-        <v>4.37</v>
+        <v>-0.18</v>
       </c>
       <c r="P9" s="3">
-        <v>7.36</v>
+        <v>67.56</v>
       </c>
       <c r="Q9" s="3">
-        <v>29.31</v>
+        <v>360.84</v>
       </c>
       <c r="R9" s="3">
-        <v>28.58</v>
-      </c>
-      <c r="S9" t="str">
+        <v>324.63</v>
+      </c>
+      <c r="S9" s="3">
+        <v>39.71</v>
+      </c>
+      <c r="T9" s="3">
+        <v>12.59</v>
+      </c>
+      <c r="U9" s="3">
+        <v>32.21</v>
+      </c>
+      <c r="V9" s="3">
+        <v>23.74</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="str">
         <v/>
       </c>
     </row>
@@ -941,57 +1103,75 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>India VIX</v>
       </c>
       <c r="C10" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D10" s="1">
-        <v>1264.7</v>
+        <v>17.16</v>
       </c>
       <c r="E10" s="2">
-        <v>0.03</v>
+        <v>1.78</v>
       </c>
       <c r="F10" s="2">
-        <v>0.03</v>
+        <v>1.78</v>
       </c>
       <c r="G10" s="2">
-        <v>-0.67</v>
+        <v>27.21</v>
       </c>
       <c r="H10" s="2">
-        <v>0.25</v>
+        <v>81.01</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>1268.34</v>
+        <v>14.95</v>
       </c>
       <c r="K10" s="1">
-        <v>1268.71</v>
+        <v>15.5</v>
       </c>
       <c r="L10" s="1">
-        <v>1281.51</v>
+        <v>12.71</v>
       </c>
       <c r="M10" s="3">
-        <v>-4.53</v>
+        <v>1.01</v>
       </c>
       <c r="N10" s="3">
-        <v>-3.79</v>
+        <v>0.79</v>
       </c>
       <c r="O10" s="3">
-        <v>1.39</v>
+        <v>0.1</v>
       </c>
       <c r="P10" s="3">
-        <v>4.98</v>
+        <v>-0.56</v>
       </c>
       <c r="Q10" s="3">
-        <v>21.48</v>
+        <v>0.1</v>
       </c>
       <c r="R10" s="3">
-        <v>21.99</v>
-      </c>
-      <c r="S10" t="str">
+        <v>0.06</v>
+      </c>
+      <c r="S10" s="3">
+        <v>67.62</v>
+      </c>
+      <c r="T10" s="3">
+        <v>22.62</v>
+      </c>
+      <c r="U10" s="3">
+        <v>12.67</v>
+      </c>
+      <c r="V10" s="3">
+        <v>18.43</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="str">
         <v/>
       </c>
     </row>
@@ -1000,57 +1180,75 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D11" s="1">
-        <v>202.16</v>
+        <v>15658.7</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="G11" s="2">
-        <v>2.73</v>
+        <v>-2.97</v>
       </c>
       <c r="H11" s="2">
-        <v>-18.86</v>
+        <v>6.96</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>181.13</v>
+        <v>15450.11</v>
       </c>
       <c r="K11" s="1">
-        <v>199.13</v>
+        <v>15656.13</v>
       </c>
       <c r="L11" s="1">
-        <v>194.2</v>
+        <v>16304.78</v>
       </c>
       <c r="M11" s="3">
-        <v>2.5</v>
+        <v>-248.63</v>
       </c>
       <c r="N11" s="3">
-        <v>2.54</v>
+        <v>-225.63</v>
       </c>
       <c r="O11" s="3">
-        <v>11.77</v>
+        <v>116.19</v>
       </c>
       <c r="P11" s="3">
-        <v>5.66</v>
+        <v>294.04</v>
       </c>
       <c r="Q11" s="3">
-        <v>5.31</v>
+        <v>990.51</v>
       </c>
       <c r="R11" s="3">
-        <v>7.65</v>
-      </c>
-      <c r="S11" t="str">
+        <v>996.57</v>
+      </c>
+      <c r="S11" s="3">
+        <v>40.17</v>
+      </c>
+      <c r="T11" s="3">
+        <v>9.04</v>
+      </c>
+      <c r="U11" s="3">
+        <v>28.52</v>
+      </c>
+      <c r="V11" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="str">
         <v/>
       </c>
     </row>
@@ -1059,57 +1257,75 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D12" s="1">
-        <v>3486.59</v>
+        <v>25774.25</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.03</v>
+        <v>1.76</v>
       </c>
       <c r="F12" s="2">
-        <v>-0.03</v>
+        <v>1.76</v>
       </c>
       <c r="G12" s="2">
-        <v>-1</v>
+        <v>-2.51</v>
       </c>
       <c r="H12" s="2">
-        <v>-0.18</v>
+        <v>13.42</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>3495.63</v>
+        <v>24390.96</v>
       </c>
       <c r="K12" s="1">
-        <v>3491.27</v>
+        <v>25749.81</v>
       </c>
       <c r="L12" s="1">
-        <v>3539.34</v>
+        <v>26419.44</v>
       </c>
       <c r="M12" s="3">
-        <v>-16.47</v>
+        <v>-268.28</v>
       </c>
       <c r="N12" s="3">
-        <v>-14.31</v>
+        <v>-218.56</v>
       </c>
       <c r="O12" s="3">
-        <v>4.22</v>
+        <v>515.16</v>
       </c>
       <c r="P12" s="3">
-        <v>15.71</v>
+        <v>737.13</v>
       </c>
       <c r="Q12" s="3">
-        <v>120.26</v>
+        <v>1788.85</v>
       </c>
       <c r="R12" s="3">
-        <v>142.19</v>
-      </c>
-      <c r="S12" t="str">
+        <v>1610.21</v>
+      </c>
+      <c r="S12" s="3">
+        <v>43.84</v>
+      </c>
+      <c r="T12" s="3">
+        <v>10.91</v>
+      </c>
+      <c r="U12" s="3">
+        <v>24.35</v>
+      </c>
+      <c r="V12" s="3">
+        <v>30.32</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="str">
         <v/>
       </c>
     </row>
@@ -1118,57 +1334,75 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D13" s="1">
-        <v>2980.67</v>
+        <v>24078.65</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.07</v>
+        <v>1.74</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.07</v>
+        <v>1.74</v>
       </c>
       <c r="G13" s="2">
-        <v>-1.1</v>
+        <v>-5.18</v>
       </c>
       <c r="H13" s="2">
-        <v>0.46</v>
+        <v>-3.63</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>3001.37</v>
+        <v>25461.29</v>
       </c>
       <c r="K13" s="1">
-        <v>2988.3</v>
+        <v>24631.39</v>
       </c>
       <c r="L13" s="1">
-        <v>3030.94</v>
+        <v>26048.7</v>
       </c>
       <c r="M13" s="3">
-        <v>-15.04</v>
+        <v>-510.37</v>
       </c>
       <c r="N13" s="3">
-        <v>-13.48</v>
+        <v>-393.15</v>
       </c>
       <c r="O13" s="3">
-        <v>1.13</v>
+        <v>-221.51</v>
       </c>
       <c r="P13" s="3">
-        <v>11.58</v>
+        <v>119.48</v>
       </c>
       <c r="Q13" s="3">
-        <v>115.58</v>
+        <v>34.69</v>
       </c>
       <c r="R13" s="3">
-        <v>132.99</v>
-      </c>
-      <c r="S13" t="str">
+        <v>-61.51</v>
+      </c>
+      <c r="S13" s="3">
+        <v>33.08</v>
+      </c>
+      <c r="T13" s="3">
+        <v>6.99</v>
+      </c>
+      <c r="U13" s="3">
+        <v>42.11</v>
+      </c>
+      <c r="V13" s="3">
+        <v>42.21</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="str">
         <v/>
       </c>
     </row>
@@ -1177,57 +1411,75 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D14" s="1">
-        <v>3073.25</v>
+        <v>15289.05</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.09</v>
+        <v>1.63</v>
       </c>
       <c r="F14" s="2">
-        <v>-0.09</v>
+        <v>1.63</v>
       </c>
       <c r="G14" s="2">
-        <v>-1</v>
+        <v>-6.14</v>
       </c>
       <c r="H14" s="2">
-        <v>0.68</v>
+        <v>-4.47</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>3085.84</v>
+        <v>16122.23</v>
       </c>
       <c r="K14" s="1">
-        <v>3080.26</v>
+        <v>15685.11</v>
       </c>
       <c r="L14" s="1">
-        <v>3122.96</v>
+        <v>16735.81</v>
       </c>
       <c r="M14" s="3">
-        <v>-14.85</v>
+        <v>-371.75</v>
       </c>
       <c r="N14" s="3">
-        <v>-13.41</v>
+        <v>-293.22</v>
       </c>
       <c r="O14" s="3">
-        <v>3.5</v>
+        <v>-104.88</v>
       </c>
       <c r="P14" s="3">
-        <v>14.14</v>
+        <v>156.14</v>
       </c>
       <c r="Q14" s="3">
-        <v>119.5</v>
+        <v>1519.88</v>
       </c>
       <c r="R14" s="3">
-        <v>136.75</v>
-      </c>
-      <c r="S14" t="str">
+        <v>1742.31</v>
+      </c>
+      <c r="S14" s="3">
+        <v>31.85</v>
+      </c>
+      <c r="T14" s="3">
+        <v>8.29</v>
+      </c>
+      <c r="U14" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="V14" s="3">
+        <v>44.85</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="str">
         <v/>
       </c>
     </row>
@@ -1236,57 +1488,75 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D15" s="1">
-        <v>2608.21</v>
+        <v>9067.1</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.11</v>
+        <v>1.6</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.11</v>
+        <v>1.6</v>
       </c>
       <c r="G15" s="2">
-        <v>-1.14</v>
+        <v>-5.87</v>
       </c>
       <c r="H15" s="2">
-        <v>-0.14</v>
+        <v>5.36</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>2632.47</v>
+        <v>8985.17</v>
       </c>
       <c r="K15" s="1">
-        <v>2615.12</v>
+        <v>9335.43</v>
       </c>
       <c r="L15" s="1">
-        <v>2653.15</v>
+        <v>9772.61</v>
       </c>
       <c r="M15" s="3">
-        <v>-13.45</v>
+        <v>-171.32</v>
       </c>
       <c r="N15" s="3">
-        <v>-12.09</v>
+        <v>-108.49</v>
       </c>
       <c r="O15" s="3">
-        <v>-1.22</v>
+        <v>119.09</v>
       </c>
       <c r="P15" s="3">
-        <v>7.61</v>
+        <v>254.91</v>
       </c>
       <c r="Q15" s="3">
-        <v>90.59</v>
+        <v>713.66</v>
       </c>
       <c r="R15" s="3">
-        <v>106.53</v>
-      </c>
-      <c r="S15" t="str">
+        <v>714.36</v>
+      </c>
+      <c r="S15" s="3">
+        <v>31.96</v>
+      </c>
+      <c r="T15" s="3">
+        <v>9.86</v>
+      </c>
+      <c r="U15" s="3">
+        <v>48.09</v>
+      </c>
+      <c r="V15" s="3">
+        <v>36.04</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="str">
         <v/>
       </c>
     </row>
@@ -1295,57 +1565,75 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D16" s="1">
-        <v>10544.4</v>
+        <v>8932.7</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.12</v>
+        <v>1.6</v>
       </c>
       <c r="F16" s="2">
-        <v>-0.12</v>
+        <v>1.6</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.66</v>
+        <v>-4.05</v>
       </c>
       <c r="H16" s="2">
-        <v>-13.79</v>
+        <v>-6.12</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>11315.17</v>
+        <v>9754.18</v>
       </c>
       <c r="K16" s="1">
-        <v>10520.12</v>
+        <v>8972.71</v>
       </c>
       <c r="L16" s="1">
-        <v>10920.58</v>
+        <v>9456.52</v>
       </c>
       <c r="M16" s="3">
-        <v>-129.66</v>
+        <v>-163.48</v>
       </c>
       <c r="N16" s="3">
-        <v>-148.15</v>
+        <v>-166.97</v>
       </c>
       <c r="O16" s="3">
-        <v>-217.36</v>
+        <v>-213.51</v>
       </c>
       <c r="P16" s="3">
-        <v>-158.68</v>
+        <v>-97.78</v>
       </c>
       <c r="Q16" s="3">
-        <v>81.1</v>
+        <v>388.24</v>
       </c>
       <c r="R16" s="3">
-        <v>281.02</v>
-      </c>
-      <c r="S16" t="str">
+        <v>508.01</v>
+      </c>
+      <c r="S16" s="3">
+        <v>38.67</v>
+      </c>
+      <c r="T16" s="3">
+        <v>12.62</v>
+      </c>
+      <c r="U16" s="3">
+        <v>32.95</v>
+      </c>
+      <c r="V16" s="3">
+        <v>42.34</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="str">
         <v/>
       </c>
     </row>
@@ -1354,57 +1642,75 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D17" s="1">
-        <v>842.03</v>
+        <v>47530.5</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.18</v>
+        <v>1.59</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.18</v>
+        <v>1.59</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.54</v>
+        <v>-4.13</v>
       </c>
       <c r="H17" s="2">
-        <v>-5.54</v>
+        <v>-0.07</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>874.39</v>
+        <v>49076.85</v>
       </c>
       <c r="K17" s="1">
-        <v>845.54</v>
+        <v>48480.47</v>
       </c>
       <c r="L17" s="1">
-        <v>863.12</v>
+        <v>50669.02</v>
       </c>
       <c r="M17" s="3">
-        <v>-6.21</v>
+        <v>-794.46</v>
       </c>
       <c r="N17" s="3">
-        <v>-5.74</v>
+        <v>-581.38</v>
       </c>
       <c r="O17" s="3">
-        <v>-8.45</v>
+        <v>-191.61</v>
       </c>
       <c r="P17" s="3">
-        <v>-5.57</v>
+        <v>390.7</v>
       </c>
       <c r="Q17" s="3">
-        <v>-16.9</v>
+        <v>0.88</v>
       </c>
       <c r="R17" s="3">
-        <v>-14.13</v>
-      </c>
-      <c r="S17" t="str">
+        <v>-310.98</v>
+      </c>
+      <c r="S17" s="3">
+        <v>33.5</v>
+      </c>
+      <c r="T17" s="3">
+        <v>6.87</v>
+      </c>
+      <c r="U17" s="3">
+        <v>42.86</v>
+      </c>
+      <c r="V17" s="3">
+        <v>46.11</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="str">
         <v/>
       </c>
     </row>
@@ -1413,57 +1719,75 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D18" s="1">
-        <v>1643.9</v>
+        <v>35022.35</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.26</v>
+        <v>1.46</v>
       </c>
       <c r="F18" s="2">
-        <v>-0.26</v>
+        <v>1.46</v>
       </c>
       <c r="G18" s="2">
-        <v>3.83</v>
+        <v>-4.4</v>
       </c>
       <c r="H18" s="2">
-        <v>13.79</v>
+        <v>-0.86</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>1467.11</v>
+        <v>37719.99</v>
       </c>
       <c r="K18" s="1">
-        <v>1612.22</v>
+        <v>35548.44</v>
       </c>
       <c r="L18" s="1">
-        <v>1572.07</v>
+        <v>37253.89</v>
       </c>
       <c r="M18" s="3">
-        <v>21.7</v>
+        <v>-636.01</v>
       </c>
       <c r="N18" s="3">
-        <v>12.12</v>
+        <v>-539.82</v>
       </c>
       <c r="O18" s="3">
-        <v>37.41</v>
+        <v>-704.61</v>
       </c>
       <c r="P18" s="3">
-        <v>32.59</v>
+        <v>-210.95</v>
       </c>
       <c r="Q18" s="3">
-        <v>-68.54</v>
+        <v>929.96</v>
       </c>
       <c r="R18" s="3">
-        <v>-104.6</v>
-      </c>
-      <c r="S18" t="str">
+        <v>1227.31</v>
+      </c>
+      <c r="S18" s="3">
+        <v>33.63</v>
+      </c>
+      <c r="T18" s="3">
+        <v>10.52</v>
+      </c>
+      <c r="U18" s="3">
+        <v>40.1</v>
+      </c>
+      <c r="V18" s="3">
+        <v>35.62</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="str">
         <v/>
       </c>
     </row>
@@ -1472,57 +1796,75 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D19" s="1">
-        <v>53699.95</v>
+        <v>8546.4</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.27</v>
+        <v>1.44</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.27</v>
+        <v>1.44</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.7</v>
+        <v>6.48</v>
       </c>
       <c r="H19" s="2">
-        <v>6.74</v>
+        <v>-9.3</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>52179.54</v>
+        <v>8247.23</v>
       </c>
       <c r="K19" s="1">
-        <v>54484.23</v>
+        <v>8458.71</v>
       </c>
       <c r="L19" s="1">
-        <v>55763.52</v>
+        <v>8522.88</v>
       </c>
       <c r="M19" s="3">
-        <v>-379.62</v>
+        <v>28.28</v>
       </c>
       <c r="N19" s="3">
-        <v>-291.78</v>
+        <v>-16.35</v>
       </c>
       <c r="O19" s="3">
-        <v>790.27</v>
+        <v>65.7</v>
       </c>
       <c r="P19" s="3">
-        <v>1172.96</v>
+        <v>59.36</v>
       </c>
       <c r="Q19" s="3">
-        <v>3756.85</v>
+        <v>374.86</v>
       </c>
       <c r="R19" s="3">
-        <v>3900.21</v>
-      </c>
-      <c r="S19" t="str">
+        <v>514.22</v>
+      </c>
+      <c r="S19" s="3">
+        <v>56.06</v>
+      </c>
+      <c r="T19" s="3">
+        <v>19.36</v>
+      </c>
+      <c r="U19" s="3">
+        <v>22.83</v>
+      </c>
+      <c r="V19" s="3">
+        <v>20.52</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="str">
         <v/>
       </c>
     </row>
@@ -1531,57 +1873,75 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D20" s="1">
-        <v>3294.03</v>
+        <v>17985</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.28</v>
+        <v>1.38</v>
       </c>
       <c r="F20" s="2">
-        <v>-0.28</v>
+        <v>1.38</v>
       </c>
       <c r="G20" s="2">
-        <v>-0.83</v>
+        <v>-6.55</v>
       </c>
       <c r="H20" s="2">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>3294.67</v>
+        <v>18189.73</v>
       </c>
       <c r="K20" s="1">
-        <v>3302.34</v>
+        <v>18588.89</v>
       </c>
       <c r="L20" s="1">
-        <v>3353.89</v>
+        <v>19542.92</v>
       </c>
       <c r="M20" s="3">
-        <v>-17.29</v>
+        <v>-379.49</v>
       </c>
       <c r="N20" s="3">
-        <v>-16.97</v>
+        <v>-237.07</v>
       </c>
       <c r="O20" s="3">
-        <v>8.25</v>
+        <v>133.48</v>
       </c>
       <c r="P20" s="3">
-        <v>21.63</v>
+        <v>408.34</v>
       </c>
       <c r="Q20" s="3">
-        <v>137.13</v>
+        <v>816.93</v>
       </c>
       <c r="R20" s="3">
-        <v>154.03</v>
-      </c>
-      <c r="S20" t="str">
+        <v>847.56</v>
+      </c>
+      <c r="S20" s="3">
+        <v>29.34</v>
+      </c>
+      <c r="T20" s="3">
+        <v>9.78</v>
+      </c>
+      <c r="U20" s="3">
+        <v>50.44</v>
+      </c>
+      <c r="V20" s="3">
+        <v>37.57</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="str">
         <v/>
       </c>
     </row>
@@ -1590,57 +1950,75 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D21" s="1">
-        <v>52153.85</v>
+        <v>13352.05</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.3</v>
+        <v>1.37</v>
       </c>
       <c r="F21" s="2">
-        <v>-0.3</v>
+        <v>1.37</v>
       </c>
       <c r="G21" s="2">
-        <v>-1.4</v>
+        <v>-2.89</v>
       </c>
       <c r="H21" s="2">
-        <v>-1.05</v>
+        <v>-7.73</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>52561.74</v>
+        <v>14136.78</v>
       </c>
       <c r="K21" s="1">
-        <v>52721.92</v>
+        <v>13435.21</v>
       </c>
       <c r="L21" s="1">
-        <v>54265.33</v>
+        <v>14083.08</v>
       </c>
       <c r="M21" s="3">
-        <v>-513.88</v>
+        <v>-214.3</v>
       </c>
       <c r="N21" s="3">
-        <v>-448.09</v>
+        <v>-209.52</v>
       </c>
       <c r="O21" s="3">
-        <v>119.23</v>
+        <v>-215.84</v>
       </c>
       <c r="P21" s="3">
-        <v>462.24</v>
+        <v>-57.34</v>
       </c>
       <c r="Q21" s="3">
-        <v>-663.92</v>
+        <v>72.84</v>
       </c>
       <c r="R21" s="3">
-        <v>-1104.48</v>
-      </c>
-      <c r="S21" t="str">
+        <v>117.75</v>
+      </c>
+      <c r="S21" s="3">
+        <v>37.58</v>
+      </c>
+      <c r="T21" s="3">
+        <v>11.09</v>
+      </c>
+      <c r="U21" s="3">
+        <v>34.87</v>
+      </c>
+      <c r="V21" s="3">
+        <v>45.41</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="str">
         <v/>
       </c>
     </row>
@@ -1649,57 +2027,75 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C22" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D22" s="1">
-        <v>68695.85</v>
+        <v>15286.05</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.42</v>
+        <v>1.35</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.42</v>
+        <v>1.35</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.51</v>
+        <v>-4.56</v>
       </c>
       <c r="H22" s="2">
-        <v>-0.96</v>
+        <v>-4.31</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>70047.92</v>
+        <v>16000.49</v>
       </c>
       <c r="K22" s="1">
-        <v>68969.8</v>
+        <v>15483.98</v>
       </c>
       <c r="L22" s="1">
-        <v>71956.6</v>
+        <v>16347.16</v>
       </c>
       <c r="M22" s="3">
-        <v>-936.03</v>
+        <v>-290.59</v>
       </c>
       <c r="N22" s="3">
-        <v>-988.8</v>
+        <v>-261.9</v>
       </c>
       <c r="O22" s="3">
-        <v>-115.29</v>
+        <v>-126.04</v>
       </c>
       <c r="P22" s="3">
-        <v>595.35</v>
+        <v>79.96</v>
       </c>
       <c r="Q22" s="3">
-        <v>2746.93</v>
+        <v>349.56</v>
       </c>
       <c r="R22" s="3">
-        <v>3199.01</v>
-      </c>
-      <c r="S22" t="str">
+        <v>326.8</v>
+      </c>
+      <c r="S22" s="3">
+        <v>34.48</v>
+      </c>
+      <c r="T22" s="3">
+        <v>8.13</v>
+      </c>
+      <c r="U22" s="3">
+        <v>38.96</v>
+      </c>
+      <c r="V22" s="3">
+        <v>48.97</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="str">
         <v/>
       </c>
     </row>
@@ -1708,57 +2104,75 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D23" s="1">
-        <v>12066.4</v>
+        <v>10520.95</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.55</v>
+        <v>1.35</v>
       </c>
       <c r="F23" s="2">
-        <v>-0.55</v>
+        <v>1.35</v>
       </c>
       <c r="G23" s="2">
-        <v>-5.44</v>
+        <v>-0.88</v>
       </c>
       <c r="H23" s="2">
-        <v>8.05</v>
+        <v>-13.98</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>12472.86</v>
+        <v>11282.93</v>
       </c>
       <c r="K23" s="1">
-        <v>12170.45</v>
+        <v>10492.06</v>
       </c>
       <c r="L23" s="1">
-        <v>12892.37</v>
+        <v>10855.13</v>
       </c>
       <c r="M23" s="3">
-        <v>-269.43</v>
+        <v>-109.89</v>
       </c>
       <c r="N23" s="3">
-        <v>-239.21</v>
+        <v>-129.34</v>
       </c>
       <c r="O23" s="3">
-        <v>31.91</v>
+        <v>-233.14</v>
       </c>
       <c r="P23" s="3">
-        <v>212.27</v>
+        <v>-175.66</v>
       </c>
       <c r="Q23" s="3">
-        <v>1154.3</v>
+        <v>79.23</v>
       </c>
       <c r="R23" s="3">
-        <v>1133.55</v>
-      </c>
-      <c r="S23" t="str">
+        <v>280.64</v>
+      </c>
+      <c r="S23" s="3">
+        <v>45.04</v>
+      </c>
+      <c r="T23" s="3">
+        <v>17.68</v>
+      </c>
+      <c r="U23" s="3">
+        <v>29.63</v>
+      </c>
+      <c r="V23" s="3">
+        <v>31.06</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="str">
         <v/>
       </c>
     </row>
@@ -1767,57 +2181,75 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D24" s="1">
-        <v>6031.35</v>
+        <v>16020.75</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.56</v>
+        <v>1.31</v>
       </c>
       <c r="F24" s="2">
-        <v>-0.56</v>
+        <v>1.31</v>
       </c>
       <c r="G24" s="2">
-        <v>-3.17</v>
+        <v>0.69</v>
       </c>
       <c r="H24" s="2">
-        <v>-5.25</v>
+        <v>-27.17</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>6748.38</v>
+        <v>18338.84</v>
       </c>
       <c r="K24" s="1">
-        <v>6081.57</v>
+        <v>16035.88</v>
       </c>
       <c r="L24" s="1">
-        <v>6324.49</v>
+        <v>17028.08</v>
       </c>
       <c r="M24" s="3">
-        <v>-92.33</v>
+        <v>-259.06</v>
       </c>
       <c r="N24" s="3">
-        <v>-91.23</v>
+        <v>-334.02</v>
       </c>
       <c r="O24" s="3">
-        <v>-197.33</v>
+        <v>-707.92</v>
       </c>
       <c r="P24" s="3">
-        <v>-145.89</v>
+        <v>-553.7</v>
       </c>
       <c r="Q24" s="3">
-        <v>235.3</v>
+        <v>264.11</v>
       </c>
       <c r="R24" s="3">
-        <v>404.21</v>
-      </c>
-      <c r="S24" t="str">
+        <v>926.62</v>
+      </c>
+      <c r="S24" s="3">
+        <v>45.04</v>
+      </c>
+      <c r="T24" s="3">
+        <v>12</v>
+      </c>
+      <c r="U24" s="3">
+        <v>26.39</v>
+      </c>
+      <c r="V24" s="3">
+        <v>38.22</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="str">
         <v/>
       </c>
     </row>
@@ -1826,57 +2258,75 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D25" s="1">
-        <v>28924.95</v>
+        <v>10501.1</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.57</v>
+        <v>1.31</v>
       </c>
       <c r="F25" s="2">
-        <v>-0.57</v>
+        <v>1.31</v>
       </c>
       <c r="G25" s="2">
-        <v>-2.01</v>
+        <v>0.63</v>
       </c>
       <c r="H25" s="2">
-        <v>-7.14</v>
+        <v>-28.57</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>30414.07</v>
+        <v>12150.78</v>
       </c>
       <c r="K25" s="1">
-        <v>29261.63</v>
+        <v>10513.55</v>
       </c>
       <c r="L25" s="1">
-        <v>30395.42</v>
+        <v>11170.09</v>
       </c>
       <c r="M25" s="3">
-        <v>-375.34</v>
+        <v>-172.67</v>
       </c>
       <c r="N25" s="3">
-        <v>-355.55</v>
+        <v>-221.68</v>
       </c>
       <c r="O25" s="3">
-        <v>-301.38</v>
+        <v>-508.08</v>
       </c>
       <c r="P25" s="3">
-        <v>-78.74</v>
+        <v>-412.2</v>
       </c>
       <c r="Q25" s="3">
-        <v>1491.04</v>
+        <v>-14.94</v>
       </c>
       <c r="R25" s="3">
-        <v>2007.93</v>
-      </c>
-      <c r="S25" t="str">
+        <v>424.43</v>
+      </c>
+      <c r="S25" s="3">
+        <v>44.9</v>
+      </c>
+      <c r="T25" s="3">
+        <v>11.91</v>
+      </c>
+      <c r="U25" s="3">
+        <v>26.45</v>
+      </c>
+      <c r="V25" s="3">
+        <v>38.6</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="str">
         <v/>
       </c>
     </row>
@@ -1885,57 +2335,75 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D26" s="1">
-        <v>5598.5</v>
+        <v>16266.85</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.59</v>
+        <v>1.25</v>
       </c>
       <c r="F26" s="2">
-        <v>-0.59</v>
+        <v>1.25</v>
       </c>
       <c r="G26" s="2">
-        <v>2.3</v>
+        <v>-4.47</v>
       </c>
       <c r="H26" s="2">
-        <v>-12.32</v>
+        <v>-5.72</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>5960.48</v>
+        <v>17213.81</v>
       </c>
       <c r="K26" s="1">
-        <v>5529.85</v>
+        <v>16577.97</v>
       </c>
       <c r="L26" s="1">
-        <v>5706.91</v>
+        <v>17593.24</v>
       </c>
       <c r="M26" s="3">
-        <v>-39.72</v>
+        <v>-346.52</v>
       </c>
       <c r="N26" s="3">
-        <v>-71.03</v>
+        <v>-303.9</v>
       </c>
       <c r="O26" s="3">
-        <v>-115.29</v>
+        <v>-162.68</v>
       </c>
       <c r="P26" s="3">
-        <v>-95.05</v>
+        <v>90.36</v>
       </c>
       <c r="Q26" s="3">
-        <v>28.8</v>
+        <v>875.97</v>
       </c>
       <c r="R26" s="3">
-        <v>140.24</v>
-      </c>
-      <c r="S26" t="str">
+        <v>1043.44</v>
+      </c>
+      <c r="S26" s="3">
+        <v>31.26</v>
+      </c>
+      <c r="T26" s="3">
+        <v>7.43</v>
+      </c>
+      <c r="U26" s="3">
+        <v>40.47</v>
+      </c>
+      <c r="V26" s="3">
+        <v>49.72</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="str">
         <v/>
       </c>
     </row>
@@ -1944,57 +2412,75 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C27" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D27" s="1">
-        <v>35974.45</v>
+        <v>8661.2</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.6</v>
+        <v>1.25</v>
       </c>
       <c r="F27" s="2">
-        <v>-0.6</v>
+        <v>1.25</v>
       </c>
       <c r="G27" s="2">
-        <v>-1.81</v>
+        <v>-0.83</v>
       </c>
       <c r="H27" s="2">
-        <v>1.84</v>
+        <v>-9.93</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>37721.97</v>
+        <v>9216.09</v>
       </c>
       <c r="K27" s="1">
-        <v>36241.05</v>
+        <v>8635.93</v>
       </c>
       <c r="L27" s="1">
-        <v>37551.17</v>
+        <v>8981.47</v>
       </c>
       <c r="M27" s="3">
-        <v>-461.17</v>
+        <v>-103.57</v>
       </c>
       <c r="N27" s="3">
-        <v>-471.75</v>
+        <v>-121.84</v>
       </c>
       <c r="O27" s="3">
-        <v>-476.48</v>
+        <v>-175.63</v>
       </c>
       <c r="P27" s="3">
-        <v>-64.34</v>
+        <v>-99.59</v>
       </c>
       <c r="Q27" s="3">
-        <v>1005.91</v>
+        <v>272.56</v>
       </c>
       <c r="R27" s="3">
-        <v>1242.5</v>
-      </c>
-      <c r="S27" t="str">
+        <v>433.9</v>
+      </c>
+      <c r="S27" s="3">
+        <v>44.47</v>
+      </c>
+      <c r="T27" s="3">
+        <v>15.55</v>
+      </c>
+      <c r="U27" s="3">
+        <v>28.03</v>
+      </c>
+      <c r="V27" s="3">
+        <v>41.53</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="str">
         <v/>
       </c>
     </row>
@@ -2003,57 +2489,75 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D28" s="1">
-        <v>9525.85</v>
+        <v>56465.4</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.6</v>
+        <v>1.19</v>
       </c>
       <c r="F28" s="2">
-        <v>-0.6</v>
+        <v>1.19</v>
       </c>
       <c r="G28" s="2">
-        <v>-1.11</v>
+        <v>-4.83</v>
       </c>
       <c r="H28" s="2">
-        <v>10.69</v>
+        <v>-6.64</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>8973.96</v>
+        <v>60273.79</v>
       </c>
       <c r="K28" s="1">
-        <v>9620.27</v>
+        <v>57749.53</v>
       </c>
       <c r="L28" s="1">
-        <v>9837.16</v>
+        <v>61265.6</v>
       </c>
       <c r="M28" s="3">
-        <v>-70.49</v>
+        <v>-1218.17</v>
       </c>
       <c r="N28" s="3">
-        <v>-62.77</v>
+        <v>-1020.65</v>
       </c>
       <c r="O28" s="3">
-        <v>219.67</v>
+        <v>-703.37</v>
       </c>
       <c r="P28" s="3">
-        <v>298.45</v>
+        <v>176.31</v>
       </c>
       <c r="Q28" s="3">
-        <v>750.26</v>
+        <v>2781.02</v>
       </c>
       <c r="R28" s="3">
-        <v>721.68</v>
-      </c>
-      <c r="S28" t="str">
+        <v>3462.12</v>
+      </c>
+      <c r="S28" s="3">
+        <v>30.24</v>
+      </c>
+      <c r="T28" s="3">
+        <v>6.72</v>
+      </c>
+      <c r="U28" s="3">
+        <v>44.13</v>
+      </c>
+      <c r="V28" s="3">
+        <v>51.82</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="str">
         <v/>
       </c>
     </row>
@@ -2062,57 +2566,75 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C29" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D29" s="1">
-        <v>9190.6</v>
+        <v>8661.95</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.61</v>
+        <v>1.18</v>
       </c>
       <c r="F29" s="2">
-        <v>-0.61</v>
+        <v>1.18</v>
       </c>
       <c r="G29" s="2">
-        <v>-1.81</v>
+        <v>-6.63</v>
       </c>
       <c r="H29" s="2">
-        <v>-6.73</v>
+        <v>11.8</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>9995.43</v>
+        <v>8847.33</v>
       </c>
       <c r="K29" s="1">
-        <v>9232.39</v>
+        <v>8922.78</v>
       </c>
       <c r="L29" s="1">
-        <v>9571.2</v>
+        <v>9436.77</v>
       </c>
       <c r="M29" s="3">
-        <v>-116.71</v>
+        <v>-178.05</v>
       </c>
       <c r="N29" s="3">
-        <v>-127.3</v>
+        <v>-130.67</v>
       </c>
       <c r="O29" s="3">
-        <v>-220.01</v>
+        <v>29.55</v>
       </c>
       <c r="P29" s="3">
-        <v>-145.27</v>
+        <v>190.65</v>
       </c>
       <c r="Q29" s="3">
-        <v>800.38</v>
+        <v>591.12</v>
       </c>
       <c r="R29" s="3">
-        <v>1093.5</v>
-      </c>
-      <c r="S29" t="str">
+        <v>520.33</v>
+      </c>
+      <c r="S29" s="3">
+        <v>33.74</v>
+      </c>
+      <c r="T29" s="3">
+        <v>13.05</v>
+      </c>
+      <c r="U29" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="V29" s="3">
+        <v>29.08</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="str">
         <v/>
       </c>
     </row>
@@ -2121,57 +2643,75 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D30" s="1">
-        <v>25046.05</v>
+        <v>16570.5</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.63</v>
+        <v>1.13</v>
       </c>
       <c r="F30" s="2">
-        <v>-0.63</v>
+        <v>1.13</v>
       </c>
       <c r="G30" s="2">
-        <v>-1.37</v>
+        <v>-6.9</v>
       </c>
       <c r="H30" s="2">
-        <v>0.24</v>
+        <v>-0.68</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>25476.47</v>
+        <v>16948.59</v>
       </c>
       <c r="K30" s="1">
-        <v>25301.13</v>
+        <v>17125.03</v>
       </c>
       <c r="L30" s="1">
-        <v>26266.15</v>
+        <v>18007.55</v>
       </c>
       <c r="M30" s="3">
-        <v>-308.66</v>
+        <v>-349.8</v>
       </c>
       <c r="N30" s="3">
-        <v>-307.25</v>
+        <v>-227.08</v>
       </c>
       <c r="O30" s="3">
-        <v>-1.77</v>
+        <v>54.88</v>
       </c>
       <c r="P30" s="3">
-        <v>226.74</v>
+        <v>309.15</v>
       </c>
       <c r="Q30" s="3">
-        <v>111.86</v>
+        <v>1270.26</v>
       </c>
       <c r="R30" s="3">
-        <v>-46.08</v>
-      </c>
-      <c r="S30" t="str">
+        <v>1421.29</v>
+      </c>
+      <c r="S30" s="3">
+        <v>27.78</v>
+      </c>
+      <c r="T30" s="3">
+        <v>9.24</v>
+      </c>
+      <c r="U30" s="3">
+        <v>50.67</v>
+      </c>
+      <c r="V30" s="3">
+        <v>40.23</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="str">
         <v/>
       </c>
     </row>
@@ -2180,57 +2720,75 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D31" s="1">
-        <v>15078.3</v>
+        <v>8984.95</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.63</v>
+        <v>1.12</v>
       </c>
       <c r="F31" s="2">
-        <v>-0.63</v>
+        <v>1.12</v>
       </c>
       <c r="G31" s="2">
-        <v>-2.43</v>
+        <v>-4.01</v>
       </c>
       <c r="H31" s="2">
-        <v>-2.17</v>
+        <v>-8.82</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>15633.9</v>
+        <v>9979.7</v>
       </c>
       <c r="K31" s="1">
-        <v>15166.49</v>
+        <v>9097.99</v>
       </c>
       <c r="L31" s="1">
-        <v>15964.18</v>
+        <v>9501.72</v>
       </c>
       <c r="M31" s="3">
-        <v>-254.6</v>
+        <v>-144.02</v>
       </c>
       <c r="N31" s="3">
-        <v>-263.86</v>
+        <v>-132.09</v>
       </c>
       <c r="O31" s="3">
-        <v>-74.41</v>
+        <v>-262.81</v>
       </c>
       <c r="P31" s="3">
-        <v>105.38</v>
+        <v>-172.67</v>
       </c>
       <c r="Q31" s="3">
-        <v>1265.85</v>
+        <v>783.98</v>
       </c>
       <c r="R31" s="3">
-        <v>1447.65</v>
-      </c>
-      <c r="S31" t="str">
+        <v>1090.22</v>
+      </c>
+      <c r="S31" s="3">
+        <v>34.8</v>
+      </c>
+      <c r="T31" s="3">
+        <v>7.78</v>
+      </c>
+      <c r="U31" s="3">
+        <v>37.04</v>
+      </c>
+      <c r="V31" s="3">
+        <v>49.43</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="str">
         <v/>
       </c>
     </row>
@@ -2239,57 +2797,75 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C32" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D32" s="1">
-        <v>55488.1</v>
+        <v>19279.45</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.64</v>
+        <v>1.09</v>
       </c>
       <c r="F32" s="2">
-        <v>-0.64</v>
+        <v>1.09</v>
       </c>
       <c r="G32" s="2">
-        <v>1.57</v>
+        <v>-5.56</v>
       </c>
       <c r="H32" s="2">
-        <v>-6.87</v>
+        <v>-4.64</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>56910.46</v>
+        <v>20254.67</v>
       </c>
       <c r="K32" s="1">
-        <v>55393.42</v>
+        <v>19775.77</v>
       </c>
       <c r="L32" s="1">
-        <v>56433.5</v>
+        <v>20894.85</v>
       </c>
       <c r="M32" s="3">
-        <v>-244.5</v>
+        <v>-405.83</v>
       </c>
       <c r="N32" s="3">
-        <v>-408.33</v>
+        <v>-315.68</v>
       </c>
       <c r="O32" s="3">
-        <v>-306.23</v>
+        <v>-128.29</v>
       </c>
       <c r="P32" s="3">
-        <v>-90.13</v>
+        <v>166.12</v>
       </c>
       <c r="Q32" s="3">
-        <v>1705.86</v>
+        <v>1539.23</v>
       </c>
       <c r="R32" s="3">
-        <v>2296.75</v>
-      </c>
-      <c r="S32" t="str">
+        <v>1815.59</v>
+      </c>
+      <c r="S32" s="3">
+        <v>28.75</v>
+      </c>
+      <c r="T32" s="3">
+        <v>7.21</v>
+      </c>
+      <c r="U32" s="3">
+        <v>48.91</v>
+      </c>
+      <c r="V32" s="3">
+        <v>50.11</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="str">
         <v/>
       </c>
     </row>
@@ -2298,57 +2874,75 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D33" s="1">
-        <v>24753.65</v>
+        <v>21963.15</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.64</v>
+        <v>1.08</v>
       </c>
       <c r="F33" s="2">
-        <v>-0.64</v>
+        <v>1.08</v>
       </c>
       <c r="G33" s="2">
-        <v>-1.85</v>
+        <v>-3.53</v>
       </c>
       <c r="H33" s="2">
-        <v>-8.58</v>
+        <v>-8.71</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>26278.33</v>
+        <v>23471.33</v>
       </c>
       <c r="K33" s="1">
-        <v>24891.72</v>
+        <v>22428.13</v>
       </c>
       <c r="L33" s="1">
-        <v>26249.17</v>
+        <v>23606.7</v>
       </c>
       <c r="M33" s="3">
-        <v>-435.9</v>
+        <v>-390.95</v>
       </c>
       <c r="N33" s="3">
-        <v>-463.99</v>
+        <v>-328.12</v>
       </c>
       <c r="O33" s="3">
-        <v>-331.06</v>
+        <v>-341.26</v>
       </c>
       <c r="P33" s="3">
-        <v>-64.27</v>
+        <v>-51.62</v>
       </c>
       <c r="Q33" s="3">
-        <v>1160.65</v>
+        <v>982.33</v>
       </c>
       <c r="R33" s="3">
-        <v>1598.86</v>
-      </c>
-      <c r="S33" t="str">
+        <v>1351.3</v>
+      </c>
+      <c r="S33" s="3">
+        <v>32.2</v>
+      </c>
+      <c r="T33" s="3">
+        <v>9.61</v>
+      </c>
+      <c r="U33" s="3">
+        <v>43.03</v>
+      </c>
+      <c r="V33" s="3">
+        <v>42.82</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="str">
         <v/>
       </c>
     </row>
@@ -2357,57 +2951,75 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>CNXPHARMA</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C34" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D34" s="1">
-        <v>25615</v>
+        <v>20812.25</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.65</v>
+        <v>1.07</v>
       </c>
       <c r="F34" s="2">
-        <v>-0.65</v>
+        <v>1.07</v>
       </c>
       <c r="G34" s="2">
-        <v>-3.11</v>
+        <v>-4.83</v>
       </c>
       <c r="H34" s="2">
-        <v>12.72</v>
+        <v>-6.57</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>24332</v>
+        <v>22168.85</v>
       </c>
       <c r="K34" s="1">
-        <v>25961.9</v>
+        <v>21261.46</v>
       </c>
       <c r="L34" s="1">
-        <v>26504.8</v>
+        <v>22520.56</v>
       </c>
       <c r="M34" s="3">
-        <v>-232.47</v>
+        <v>-436.73</v>
       </c>
       <c r="N34" s="3">
-        <v>-146.16</v>
+        <v>-369.82</v>
       </c>
       <c r="O34" s="3">
-        <v>600.81</v>
+        <v>-247.63</v>
       </c>
       <c r="P34" s="3">
-        <v>797.18</v>
+        <v>69.08</v>
       </c>
       <c r="Q34" s="3">
-        <v>1776.15</v>
+        <v>1671.77</v>
       </c>
       <c r="R34" s="3">
-        <v>1607.67</v>
-      </c>
-      <c r="S34" t="str">
+        <v>2020.97</v>
+      </c>
+      <c r="S34" s="3">
+        <v>29.69</v>
+      </c>
+      <c r="T34" s="3">
+        <v>7.04</v>
+      </c>
+      <c r="U34" s="3">
+        <v>44.35</v>
+      </c>
+      <c r="V34" s="3">
+        <v>51.31</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="str">
         <v/>
       </c>
     </row>
@@ -2416,57 +3028,75 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D35" s="1">
-        <v>9039.85</v>
+        <v>14665.7</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.66</v>
+        <v>1.03</v>
       </c>
       <c r="F35" s="2">
-        <v>-0.66</v>
+        <v>1.03</v>
       </c>
       <c r="G35" s="2">
-        <v>-2.9</v>
+        <v>-5.1</v>
       </c>
       <c r="H35" s="2">
-        <v>-5</v>
+        <v>-4.85</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>9765.12</v>
+        <v>15621.4</v>
       </c>
       <c r="K35" s="1">
-        <v>9068.56</v>
+        <v>14895.51</v>
       </c>
       <c r="L35" s="1">
-        <v>9541.65</v>
+        <v>15808.48</v>
       </c>
       <c r="M35" s="3">
-        <v>-162.81</v>
+        <v>-305.53</v>
       </c>
       <c r="N35" s="3">
-        <v>-170.28</v>
+        <v>-279.89</v>
       </c>
       <c r="O35" s="3">
-        <v>-173.46</v>
+        <v>-178.7</v>
       </c>
       <c r="P35" s="3">
-        <v>-64.9</v>
+        <v>41.4</v>
       </c>
       <c r="Q35" s="3">
-        <v>396.78</v>
+        <v>1232.94</v>
       </c>
       <c r="R35" s="3">
-        <v>509.72</v>
-      </c>
-      <c r="S35" t="str">
+        <v>1441.07</v>
+      </c>
+      <c r="S35" s="3">
+        <v>32.19</v>
+      </c>
+      <c r="T35" s="3">
+        <v>7.37</v>
+      </c>
+      <c r="U35" s="3">
+        <v>40.23</v>
+      </c>
+      <c r="V35" s="3">
+        <v>51.66</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="str">
         <v/>
       </c>
     </row>
@@ -2475,57 +3105,75 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D36" s="1">
-        <v>32625.05</v>
+        <v>13167.35</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.68</v>
+        <v>1.03</v>
       </c>
       <c r="F36" s="2">
-        <v>-0.68</v>
+        <v>1.03</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.72</v>
+        <v>-4.11</v>
       </c>
       <c r="H36" s="2">
-        <v>-3.92</v>
+        <v>-4.43</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>33702.89</v>
+        <v>13993.46</v>
       </c>
       <c r="K36" s="1">
-        <v>32686.26</v>
+        <v>13426.09</v>
       </c>
       <c r="L36" s="1">
-        <v>34069.02</v>
+        <v>14268.43</v>
       </c>
       <c r="M36" s="3">
-        <v>-413.87</v>
+        <v>-280.59</v>
       </c>
       <c r="N36" s="3">
-        <v>-478.8</v>
+        <v>-253.01</v>
       </c>
       <c r="O36" s="3">
-        <v>-214.67</v>
+        <v>-155.5</v>
       </c>
       <c r="P36" s="3">
-        <v>103.15</v>
+        <v>66.63</v>
       </c>
       <c r="Q36" s="3">
-        <v>2028.91</v>
+        <v>855.49</v>
       </c>
       <c r="R36" s="3">
-        <v>2435.7</v>
-      </c>
-      <c r="S36" t="str">
+        <v>997.79</v>
+      </c>
+      <c r="S36" s="3">
+        <v>31.33</v>
+      </c>
+      <c r="T36" s="3">
+        <v>8.01</v>
+      </c>
+      <c r="U36" s="3">
+        <v>39.54</v>
+      </c>
+      <c r="V36" s="3">
+        <v>46.82</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="str">
         <v/>
       </c>
     </row>
@@ -2534,57 +3182,75 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>CNXINFRA</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C37" t="str">
-        <v>CNXINFRA</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D37" s="1">
-        <v>8666.5</v>
+        <v>66477.15</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.68</v>
+        <v>0.99</v>
       </c>
       <c r="F37" s="2">
-        <v>-0.68</v>
+        <v>0.99</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.77</v>
+        <v>-4.69</v>
       </c>
       <c r="H37" s="2">
-        <v>-9.88</v>
+        <v>-4.16</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>9235.48</v>
+        <v>70002.76</v>
       </c>
       <c r="K37" s="1">
-        <v>8665.13</v>
+        <v>67721.76</v>
       </c>
       <c r="L37" s="1">
-        <v>9047.92</v>
+        <v>71325.64</v>
       </c>
       <c r="M37" s="3">
-        <v>-121.13</v>
+        <v>-1228.19</v>
       </c>
       <c r="N37" s="3">
-        <v>-138.2</v>
+        <v>-1071.34</v>
       </c>
       <c r="O37" s="3">
-        <v>-158.3</v>
+        <v>-615.96</v>
       </c>
       <c r="P37" s="3">
-        <v>-78.79</v>
+        <v>316.49</v>
       </c>
       <c r="Q37" s="3">
-        <v>272.98</v>
+        <v>2569.94</v>
       </c>
       <c r="R37" s="3">
-        <v>433.98</v>
-      </c>
-      <c r="S37" t="str">
+        <v>3163.61</v>
+      </c>
+      <c r="S37" s="3">
+        <v>32.44</v>
+      </c>
+      <c r="T37" s="3">
+        <v>8.06</v>
+      </c>
+      <c r="U37" s="3">
+        <v>39.56</v>
+      </c>
+      <c r="V37" s="3">
+        <v>48.98</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="str">
         <v/>
       </c>
     </row>
@@ -2593,57 +3259,75 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D38" s="1">
-        <v>25591.25</v>
+        <v>31937.4</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.69</v>
+        <v>0.94</v>
       </c>
       <c r="F38" s="2">
-        <v>-0.69</v>
+        <v>0.94</v>
       </c>
       <c r="G38" s="2">
-        <v>-2.67</v>
+        <v>-2.81</v>
       </c>
       <c r="H38" s="2">
-        <v>-9.22</v>
+        <v>-5.94</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>26954.81</v>
+        <v>33666.21</v>
       </c>
       <c r="K38" s="1">
-        <v>25514.14</v>
+        <v>32284.36</v>
       </c>
       <c r="L38" s="1">
-        <v>27441.73</v>
+        <v>33783.28</v>
       </c>
       <c r="M38" s="3">
-        <v>-557.94</v>
+        <v>-478.63</v>
       </c>
       <c r="N38" s="3">
-        <v>-651.27</v>
+        <v>-465.82</v>
       </c>
       <c r="O38" s="3">
-        <v>-250.8</v>
+        <v>-385.67</v>
       </c>
       <c r="P38" s="3">
-        <v>102.74</v>
+        <v>-7.18</v>
       </c>
       <c r="Q38" s="3">
-        <v>1507.35</v>
+        <v>1974.06</v>
       </c>
       <c r="R38" s="3">
-        <v>1816.97</v>
-      </c>
-      <c r="S38" t="str">
+        <v>2424.73</v>
+      </c>
+      <c r="S38" s="3">
+        <v>35.82</v>
+      </c>
+      <c r="T38" s="3">
+        <v>8.81</v>
+      </c>
+      <c r="U38" s="3">
+        <v>34.96</v>
+      </c>
+      <c r="V38" s="3">
+        <v>48.91</v>
+      </c>
+      <c r="W38" s="3">
+        <v>0</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="str">
         <v/>
       </c>
     </row>
@@ -2652,57 +3336,75 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D39" s="1">
-        <v>47321.65</v>
+        <v>24577.65</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.75</v>
+        <v>0.94</v>
       </c>
       <c r="F39" s="2">
-        <v>-0.75</v>
+        <v>0.94</v>
       </c>
       <c r="G39" s="2">
-        <v>-1.12</v>
+        <v>-2.55</v>
       </c>
       <c r="H39" s="2">
-        <v>7.58</v>
+        <v>-9.23</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>44905.83</v>
+        <v>26228.98</v>
       </c>
       <c r="K39" s="1">
-        <v>47713.56</v>
+        <v>24677.2</v>
       </c>
       <c r="L39" s="1">
-        <v>48453.83</v>
+        <v>26001.05</v>
       </c>
       <c r="M39" s="3">
-        <v>-244.43</v>
+        <v>-419.57</v>
       </c>
       <c r="N39" s="3">
-        <v>-212.11</v>
+        <v>-443.42</v>
       </c>
       <c r="O39" s="3">
-        <v>882.81</v>
+        <v>-421.99</v>
       </c>
       <c r="P39" s="3">
-        <v>1147.23</v>
+        <v>-140.98</v>
       </c>
       <c r="Q39" s="3">
-        <v>-226.03</v>
+        <v>1146.61</v>
       </c>
       <c r="R39" s="3">
-        <v>-997.05</v>
-      </c>
-      <c r="S39" t="str">
+        <v>1596.05</v>
+      </c>
+      <c r="S39" s="3">
+        <v>36.37</v>
+      </c>
+      <c r="T39" s="3">
+        <v>9.14</v>
+      </c>
+      <c r="U39" s="3">
+        <v>31.2</v>
+      </c>
+      <c r="V39" s="3">
+        <v>52.29</v>
+      </c>
+      <c r="W39" s="3">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="str">
         <v/>
       </c>
     </row>
@@ -2711,57 +3413,75 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D40" s="1">
-        <v>13528.95</v>
+        <v>15255.45</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.75</v>
+        <v>0.91</v>
       </c>
       <c r="F40" s="2">
-        <v>-0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G40" s="2">
-        <v>-1.61</v>
+        <v>-3.14</v>
       </c>
       <c r="H40" s="2">
-        <v>-6.51</v>
+        <v>-7.46</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>14159.07</v>
+        <v>16007.28</v>
       </c>
       <c r="K40" s="1">
-        <v>13598.82</v>
+        <v>15484.66</v>
       </c>
       <c r="L40" s="1">
-        <v>14196.36</v>
+        <v>16157.95</v>
       </c>
       <c r="M40" s="3">
-        <v>-193.83</v>
+        <v>-226.41</v>
       </c>
       <c r="N40" s="3">
-        <v>-207.46</v>
+        <v>-198.39</v>
       </c>
       <c r="O40" s="3">
-        <v>-154.36</v>
+        <v>-151.21</v>
       </c>
       <c r="P40" s="3">
-        <v>-12.01</v>
+        <v>14.65</v>
       </c>
       <c r="Q40" s="3">
-        <v>86.95</v>
+        <v>901.55</v>
       </c>
       <c r="R40" s="3">
-        <v>120.57</v>
-      </c>
-      <c r="S40" t="str">
+        <v>1145</v>
+      </c>
+      <c r="S40" s="3">
+        <v>33.72</v>
+      </c>
+      <c r="T40" s="3">
+        <v>8.24</v>
+      </c>
+      <c r="U40" s="3">
+        <v>40.56</v>
+      </c>
+      <c r="V40" s="3">
+        <v>48.39</v>
+      </c>
+      <c r="W40" s="3">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="str">
         <v/>
       </c>
     </row>
@@ -2770,57 +3490,75 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D41" s="1">
-        <v>49213.65</v>
+        <v>15345.7</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.79</v>
+        <v>0.9</v>
       </c>
       <c r="F41" s="2">
-        <v>-0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.73</v>
+        <v>-2.61</v>
       </c>
       <c r="H41" s="2">
-        <v>3.46</v>
+        <v>-8.95</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>49073.99</v>
+        <v>16279.33</v>
       </c>
       <c r="K41" s="1">
-        <v>49647.66</v>
+        <v>15532.57</v>
       </c>
       <c r="L41" s="1">
-        <v>51027.93</v>
+        <v>16239.03</v>
       </c>
       <c r="M41" s="3">
-        <v>-415.43</v>
+        <v>-228.01</v>
       </c>
       <c r="N41" s="3">
-        <v>-431.09</v>
+        <v>-215.41</v>
       </c>
       <c r="O41" s="3">
-        <v>190.45</v>
+        <v>-214.18</v>
       </c>
       <c r="P41" s="3">
-        <v>574.97</v>
+        <v>-48.33</v>
       </c>
       <c r="Q41" s="3">
-        <v>135.15</v>
+        <v>902.75</v>
       </c>
       <c r="R41" s="3">
-        <v>-284.13</v>
-      </c>
-      <c r="S41" t="str">
+        <v>1176.04</v>
+      </c>
+      <c r="S41" s="3">
+        <v>35.31</v>
+      </c>
+      <c r="T41" s="3">
+        <v>8.02</v>
+      </c>
+      <c r="U41" s="3">
+        <v>37.62</v>
+      </c>
+      <c r="V41" s="3">
+        <v>50.42</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="str">
         <v/>
       </c>
     </row>
@@ -2829,57 +3567,75 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D42" s="1">
-        <v>15660.05</v>
+        <v>44860.15</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.8</v>
+        <v>0.88</v>
       </c>
       <c r="F42" s="2">
-        <v>-0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G42" s="2">
-        <v>-2.23</v>
+        <v>-6.26</v>
       </c>
       <c r="H42" s="2">
-        <v>-1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>16012.47</v>
+        <v>44933.86</v>
       </c>
       <c r="K42" s="1">
-        <v>15758.92</v>
+        <v>46319.4</v>
       </c>
       <c r="L42" s="1">
-        <v>16493.32</v>
+        <v>48206.22</v>
       </c>
       <c r="M42" s="3">
-        <v>-233.31</v>
+        <v>-762.08</v>
       </c>
       <c r="N42" s="3">
-        <v>-241.96</v>
+        <v>-439.42</v>
       </c>
       <c r="O42" s="3">
-        <v>-23.91</v>
+        <v>408.54</v>
       </c>
       <c r="P42" s="3">
-        <v>140.68</v>
+        <v>963.1</v>
       </c>
       <c r="Q42" s="3">
-        <v>379.4</v>
+        <v>-422.39</v>
       </c>
       <c r="R42" s="3">
-        <v>332.77</v>
-      </c>
-      <c r="S42" t="str">
+        <v>-1036.32</v>
+      </c>
+      <c r="S42" s="3">
+        <v>29.96</v>
+      </c>
+      <c r="T42" s="3">
+        <v>10.36</v>
+      </c>
+      <c r="U42" s="3">
+        <v>47.55</v>
+      </c>
+      <c r="V42" s="3">
+        <v>34.81</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="str">
         <v/>
       </c>
     </row>
@@ -2888,57 +3644,75 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>CNXIT</v>
       </c>
       <c r="D43" s="1">
-        <v>15557.6</v>
+        <v>32273.05</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.8</v>
+        <v>0.87</v>
       </c>
       <c r="F43" s="2">
-        <v>-0.8</v>
+        <v>0.87</v>
       </c>
       <c r="G43" s="2">
-        <v>-3.6</v>
+        <v>16.49</v>
       </c>
       <c r="H43" s="2">
-        <v>6.27</v>
+        <v>-14.81</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>15431.78</v>
+        <v>30785.57</v>
       </c>
       <c r="K43" s="1">
-        <v>15815.79</v>
+        <v>31204.58</v>
       </c>
       <c r="L43" s="1">
-        <v>16397.36</v>
+        <v>29858.36</v>
       </c>
       <c r="M43" s="3">
-        <v>-236.97</v>
+        <v>816.78</v>
       </c>
       <c r="N43" s="3">
-        <v>-185.1</v>
+        <v>393.35</v>
       </c>
       <c r="O43" s="3">
-        <v>174.74</v>
+        <v>35.64</v>
       </c>
       <c r="P43" s="3">
-        <v>341.22</v>
+        <v>-408.51</v>
       </c>
       <c r="Q43" s="3">
-        <v>982.44</v>
+        <v>-1638.88</v>
       </c>
       <c r="R43" s="3">
-        <v>994.96</v>
-      </c>
-      <c r="S43" t="str">
+        <v>-1143.32</v>
+      </c>
+      <c r="S43" s="3">
+        <v>69.55</v>
+      </c>
+      <c r="T43" s="3">
+        <v>28.15</v>
+      </c>
+      <c r="U43" s="3">
+        <v>12.68</v>
+      </c>
+      <c r="V43" s="3">
+        <v>30.78</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="str">
         <v/>
       </c>
     </row>
@@ -2947,57 +3721,75 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D44" s="1">
-        <v>59774.7</v>
+        <v>21608.75</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.81</v>
+        <v>0.85</v>
       </c>
       <c r="F44" s="2">
-        <v>-0.81</v>
+        <v>0.85</v>
       </c>
       <c r="G44" s="2">
-        <v>-1.64</v>
+        <v>-2.1</v>
       </c>
       <c r="H44" s="2">
-        <v>-3.46</v>
+        <v>-9.48</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>61762.81</v>
+        <v>22820.53</v>
       </c>
       <c r="K44" s="1">
-        <v>60577.64</v>
+        <v>21832.09</v>
       </c>
       <c r="L44" s="1">
-        <v>62840.3</v>
+        <v>22704.36</v>
       </c>
       <c r="M44" s="3">
-        <v>-751.49</v>
+        <v>-276.82</v>
       </c>
       <c r="N44" s="3">
-        <v>-708.63</v>
+        <v>-266.44</v>
       </c>
       <c r="O44" s="3">
-        <v>-272.63</v>
+        <v>-292.68</v>
       </c>
       <c r="P44" s="3">
-        <v>235.93</v>
+        <v>-94.96</v>
       </c>
       <c r="Q44" s="3">
-        <v>-12.35</v>
+        <v>499.2</v>
       </c>
       <c r="R44" s="3">
-        <v>-175.4</v>
-      </c>
-      <c r="S44" t="str">
+        <v>801.79</v>
+      </c>
+      <c r="S44" s="3">
+        <v>37.13</v>
+      </c>
+      <c r="T44" s="3">
+        <v>9.02</v>
+      </c>
+      <c r="U44" s="3">
+        <v>36.33</v>
+      </c>
+      <c r="V44" s="3">
+        <v>48.31</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="str">
         <v/>
       </c>
     </row>
@@ -3006,57 +3798,75 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D45" s="1">
-        <v>5424.75</v>
+        <v>30618.45</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.86</v>
+        <v>0.83</v>
       </c>
       <c r="F45" s="2">
-        <v>-0.86</v>
+        <v>0.83</v>
       </c>
       <c r="G45" s="2">
-        <v>1.96</v>
+        <v>-0.93</v>
       </c>
       <c r="H45" s="2">
-        <v>-7.43</v>
+        <v>-8.14</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>5553.17</v>
+        <v>32323.71</v>
       </c>
       <c r="K45" s="1">
-        <v>5376.4</v>
+        <v>30710.79</v>
       </c>
       <c r="L45" s="1">
-        <v>5537.7</v>
+        <v>31862.83</v>
       </c>
       <c r="M45" s="3">
-        <v>-33.54</v>
+        <v>-338.27</v>
       </c>
       <c r="N45" s="3">
-        <v>-61.47</v>
+        <v>-382.38</v>
       </c>
       <c r="O45" s="3">
-        <v>-40.87</v>
+        <v>-454.43</v>
       </c>
       <c r="P45" s="3">
-        <v>-16.55</v>
+        <v>-185.6</v>
       </c>
       <c r="Q45" s="3">
-        <v>192.26</v>
+        <v>1827.63</v>
       </c>
       <c r="R45" s="3">
-        <v>262.12</v>
-      </c>
-      <c r="S45" t="str">
+        <v>2373.01</v>
+      </c>
+      <c r="S45" s="3">
+        <v>41.98</v>
+      </c>
+      <c r="T45" s="3">
+        <v>10.2</v>
+      </c>
+      <c r="U45" s="3">
+        <v>29.05</v>
+      </c>
+      <c r="V45" s="3">
+        <v>45.12</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="str">
         <v/>
       </c>
     </row>
@@ -3065,57 +3875,75 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D46" s="1">
-        <v>48866.6</v>
+        <v>12205.35</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.87</v>
+        <v>0.83</v>
       </c>
       <c r="F46" s="2">
-        <v>-0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G46" s="2">
-        <v>-4.15</v>
+        <v>-2.4</v>
       </c>
       <c r="H46" s="2">
-        <v>11.4</v>
+        <v>-8.87</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>47289.89</v>
+        <v>12850.64</v>
       </c>
       <c r="K46" s="1">
-        <v>49886.15</v>
+        <v>12345.93</v>
       </c>
       <c r="L46" s="1">
-        <v>51712.18</v>
+        <v>12841.96</v>
       </c>
       <c r="M46" s="3">
-        <v>-742.76</v>
+        <v>-160.07</v>
       </c>
       <c r="N46" s="3">
-        <v>-535.44</v>
+        <v>-149.73</v>
       </c>
       <c r="O46" s="3">
-        <v>986.94</v>
+        <v>-146.83</v>
       </c>
       <c r="P46" s="3">
-        <v>1570.37</v>
+        <v>-31.45</v>
       </c>
       <c r="Q46" s="3">
-        <v>2197.92</v>
+        <v>619.21</v>
       </c>
       <c r="R46" s="3">
-        <v>1477.16</v>
-      </c>
-      <c r="S46" t="str">
+        <v>823.92</v>
+      </c>
+      <c r="S46" s="3">
+        <v>36.29</v>
+      </c>
+      <c r="T46" s="3">
+        <v>9.04</v>
+      </c>
+      <c r="U46" s="3">
+        <v>37.33</v>
+      </c>
+      <c r="V46" s="3">
+        <v>47.72</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="str">
         <v/>
       </c>
     </row>
@@ -3124,57 +3952,75 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D47" s="1">
-        <v>7498.05</v>
+        <v>8350.05</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.88</v>
+        <v>0.83</v>
       </c>
       <c r="F47" s="2">
-        <v>-0.88</v>
+        <v>0.83</v>
       </c>
       <c r="G47" s="2">
-        <v>-2.68</v>
+        <v>3.38</v>
       </c>
       <c r="H47" s="2">
-        <v>-12.85</v>
+        <v>-16.87</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>7697.42</v>
+        <v>8755.27</v>
       </c>
       <c r="K47" s="1">
-        <v>7532.36</v>
+        <v>8296.89</v>
       </c>
       <c r="L47" s="1">
-        <v>7797.25</v>
+        <v>8382.31</v>
       </c>
       <c r="M47" s="3">
-        <v>-85.41</v>
+        <v>-1.79</v>
       </c>
       <c r="N47" s="3">
-        <v>-86.41</v>
+        <v>-30.2</v>
       </c>
       <c r="O47" s="3">
-        <v>-56.58</v>
+        <v>-152.19</v>
       </c>
       <c r="P47" s="3">
-        <v>-16.6</v>
+        <v>-157.51</v>
       </c>
       <c r="Q47" s="3">
-        <v>-294.39</v>
+        <v>-301.46</v>
       </c>
       <c r="R47" s="3">
-        <v>-246.06</v>
-      </c>
-      <c r="S47" t="str">
+        <v>-191.62</v>
+      </c>
+      <c r="S47" s="3">
+        <v>53.7</v>
+      </c>
+      <c r="T47" s="3">
+        <v>16.49</v>
+      </c>
+      <c r="U47" s="3">
+        <v>22.73</v>
+      </c>
+      <c r="V47" s="3">
+        <v>22.12</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="str">
         <v/>
       </c>
     </row>
@@ -3183,57 +4029,75 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D48" s="1">
-        <v>13827.75</v>
+        <v>12998.35</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.9</v>
+        <v>0.82</v>
       </c>
       <c r="F48" s="2">
-        <v>-0.9</v>
+        <v>0.82</v>
       </c>
       <c r="G48" s="2">
-        <v>3.56</v>
+        <v>-1.3</v>
       </c>
       <c r="H48" s="2">
-        <v>-9.58</v>
+        <v>-10.56</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>14407.78</v>
+        <v>13777.21</v>
       </c>
       <c r="K48" s="1">
-        <v>13643.53</v>
+        <v>13089.54</v>
       </c>
       <c r="L48" s="1">
-        <v>14077.98</v>
+        <v>13584.05</v>
       </c>
       <c r="M48" s="3">
-        <v>-87.76</v>
+        <v>-148.8</v>
       </c>
       <c r="N48" s="3">
-        <v>-177.27</v>
+        <v>-155.22</v>
       </c>
       <c r="O48" s="3">
-        <v>-209.7</v>
+        <v>-204.09</v>
       </c>
       <c r="P48" s="3">
-        <v>-159.38</v>
+        <v>-97.79</v>
       </c>
       <c r="Q48" s="3">
-        <v>-529.62</v>
+        <v>263.85</v>
       </c>
       <c r="R48" s="3">
-        <v>-490.47</v>
-      </c>
-      <c r="S48" t="str">
+        <v>463.16</v>
+      </c>
+      <c r="S48" s="3">
+        <v>39.76</v>
+      </c>
+      <c r="T48" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="U48" s="3">
+        <v>32.83</v>
+      </c>
+      <c r="V48" s="3">
+        <v>47.18</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="str">
         <v/>
       </c>
     </row>
@@ -3242,57 +4106,75 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D49" s="1">
-        <v>30908.4</v>
+        <v>7340</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.93</v>
+        <v>0.78</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.93</v>
+        <v>0.78</v>
       </c>
       <c r="G49" s="2">
-        <v>0.01</v>
+        <v>3.73</v>
       </c>
       <c r="H49" s="2">
-        <v>-7.27</v>
+        <v>-2.94</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>32376.25</v>
+        <v>7332.17</v>
       </c>
       <c r="K49" s="1">
-        <v>30895.21</v>
+        <v>7302.63</v>
       </c>
       <c r="L49" s="1">
-        <v>32105.82</v>
+        <v>7388.14</v>
       </c>
       <c r="M49" s="3">
-        <v>-349.66</v>
+        <v>1.25</v>
       </c>
       <c r="N49" s="3">
-        <v>-440.21</v>
+        <v>-25.39</v>
       </c>
       <c r="O49" s="3">
-        <v>-363.4</v>
+        <v>-4.58</v>
       </c>
       <c r="P49" s="3">
-        <v>-109.75</v>
+        <v>23.59</v>
       </c>
       <c r="Q49" s="3">
-        <v>1850.76</v>
+        <v>471.2</v>
       </c>
       <c r="R49" s="3">
-        <v>2377.64</v>
-      </c>
-      <c r="S49" t="str">
+        <v>552.45</v>
+      </c>
+      <c r="S49" s="3">
+        <v>52.82</v>
+      </c>
+      <c r="T49" s="3">
+        <v>17.79</v>
+      </c>
+      <c r="U49" s="3">
+        <v>24.32</v>
+      </c>
+      <c r="V49" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="str">
         <v/>
       </c>
     </row>
@@ -3301,57 +4183,75 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C50" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D50" s="1">
-        <v>29239.8</v>
+        <v>30162.5</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.93</v>
+        <v>0.76</v>
       </c>
       <c r="F50" s="2">
-        <v>-0.93</v>
+        <v>0.76</v>
       </c>
       <c r="G50" s="2">
-        <v>-3.61</v>
+        <v>3.96</v>
       </c>
       <c r="H50" s="2">
-        <v>-4.35</v>
+        <v>-10.38</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>31419.18</v>
+        <v>30923.89</v>
       </c>
       <c r="K50" s="1">
-        <v>29759.56</v>
+        <v>29883.33</v>
       </c>
       <c r="L50" s="1">
-        <v>31753.46</v>
+        <v>30063.06</v>
       </c>
       <c r="M50" s="3">
-        <v>-646.57</v>
+        <v>50.49</v>
       </c>
       <c r="N50" s="3">
-        <v>-629.11</v>
+        <v>-89.45</v>
       </c>
       <c r="O50" s="3">
-        <v>-404.61</v>
+        <v>-327.11</v>
       </c>
       <c r="P50" s="3">
-        <v>84.87</v>
+        <v>-319.35</v>
       </c>
       <c r="Q50" s="3">
-        <v>2038.85</v>
+        <v>500.28</v>
       </c>
       <c r="R50" s="3">
-        <v>2407.67</v>
-      </c>
-      <c r="S50" t="str">
+        <v>994.55</v>
+      </c>
+      <c r="S50" s="3">
+        <v>56.23</v>
+      </c>
+      <c r="T50" s="3">
+        <v>17.61</v>
+      </c>
+      <c r="U50" s="3">
+        <v>21.98</v>
+      </c>
+      <c r="V50" s="3">
+        <v>25.96</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="str">
         <v/>
       </c>
     </row>
@@ -3360,57 +4260,75 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D51" s="1">
-        <v>18743.65</v>
+        <v>23637.1</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.93</v>
+        <v>0.73</v>
       </c>
       <c r="F51" s="2">
-        <v>-0.93</v>
+        <v>0.73</v>
       </c>
       <c r="G51" s="2">
-        <v>-0.22</v>
+        <v>-0.41</v>
       </c>
       <c r="H51" s="2">
-        <v>-11.29</v>
+        <v>-11.44</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>19890.8</v>
+        <v>25008.19</v>
       </c>
       <c r="K51" s="1">
-        <v>18774.85</v>
+        <v>23713.09</v>
       </c>
       <c r="L51" s="1">
-        <v>19583.61</v>
+        <v>24474</v>
       </c>
       <c r="M51" s="3">
-        <v>-232.6</v>
+        <v>-212.77</v>
       </c>
       <c r="N51" s="3">
-        <v>-284.84</v>
+        <v>-247.22</v>
       </c>
       <c r="O51" s="3">
-        <v>-295.29</v>
+        <v>-389.01</v>
       </c>
       <c r="P51" s="3">
-        <v>-144.6</v>
+        <v>-237.74</v>
       </c>
       <c r="Q51" s="3">
-        <v>760.52</v>
+        <v>323.97</v>
       </c>
       <c r="R51" s="3">
-        <v>1111.92</v>
-      </c>
-      <c r="S51" t="str">
+        <v>706.96</v>
+      </c>
+      <c r="S51" s="3">
+        <v>42.99</v>
+      </c>
+      <c r="T51" s="3">
+        <v>10.94</v>
+      </c>
+      <c r="U51" s="3">
+        <v>29.31</v>
+      </c>
+      <c r="V51" s="3">
+        <v>43.4</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="str">
         <v/>
       </c>
     </row>
@@ -3419,57 +4337,75 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D52" s="1">
-        <v>9124.3</v>
+        <v>5340.6</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.94</v>
+        <v>0.73</v>
       </c>
       <c r="F52" s="2">
-        <v>-0.94</v>
+        <v>0.73</v>
       </c>
       <c r="G52" s="2">
-        <v>-1.64</v>
+        <v>0.38</v>
       </c>
       <c r="H52" s="2">
-        <v>17.77</v>
+        <v>-8.86</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>8827.02</v>
+        <v>5543.38</v>
       </c>
       <c r="K52" s="1">
-        <v>9190.46</v>
+        <v>5359.87</v>
       </c>
       <c r="L52" s="1">
-        <v>9511</v>
+        <v>5502.51</v>
       </c>
       <c r="M52" s="3">
-        <v>-89.98</v>
+        <v>-31.23</v>
       </c>
       <c r="N52" s="3">
-        <v>-101.8</v>
+        <v>-42.96</v>
       </c>
       <c r="O52" s="3">
-        <v>126.12</v>
+        <v>-55.6</v>
       </c>
       <c r="P52" s="3">
-        <v>239.91</v>
+        <v>-25.92</v>
       </c>
       <c r="Q52" s="3">
-        <v>628</v>
+        <v>185.54</v>
       </c>
       <c r="R52" s="3">
-        <v>527.7</v>
-      </c>
-      <c r="S52" t="str">
+        <v>260.77</v>
+      </c>
+      <c r="S52" s="3">
+        <v>45.16</v>
+      </c>
+      <c r="T52" s="3">
+        <v>13.78</v>
+      </c>
+      <c r="U52" s="3">
+        <v>29.82</v>
+      </c>
+      <c r="V52" s="3">
+        <v>38.84</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="str">
         <v/>
       </c>
     </row>
@@ -3478,57 +4414,75 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D53" s="1">
-        <v>10919.1</v>
+        <v>10804.45</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.96</v>
+        <v>0.72</v>
       </c>
       <c r="F53" s="2">
-        <v>-0.96</v>
+        <v>0.72</v>
       </c>
       <c r="G53" s="2">
-        <v>3.6</v>
+        <v>-2.42</v>
       </c>
       <c r="H53" s="2">
-        <v>-12.53</v>
+        <v>-12.08</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>11239.26</v>
+        <v>11481.78</v>
       </c>
       <c r="K53" s="1">
-        <v>10717.61</v>
+        <v>10869.26</v>
       </c>
       <c r="L53" s="1">
-        <v>11122.31</v>
+        <v>11422.64</v>
       </c>
       <c r="M53" s="3">
-        <v>-79.61</v>
+        <v>-171.64</v>
       </c>
       <c r="N53" s="3">
-        <v>-160.82</v>
+        <v>-178.62</v>
       </c>
       <c r="O53" s="3">
-        <v>-112.2</v>
+        <v>-185.64</v>
       </c>
       <c r="P53" s="3">
-        <v>-75.56</v>
+        <v>-71.67</v>
       </c>
       <c r="Q53" s="3">
-        <v>33.84</v>
+        <v>214.86</v>
       </c>
       <c r="R53" s="3">
-        <v>177.01</v>
-      </c>
-      <c r="S53" t="str">
+        <v>393.64</v>
+      </c>
+      <c r="S53" s="3">
+        <v>38.41</v>
+      </c>
+      <c r="T53" s="3">
+        <v>9.47</v>
+      </c>
+      <c r="U53" s="3">
+        <v>33.19</v>
+      </c>
+      <c r="V53" s="3">
+        <v>48.08</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="str">
         <v/>
       </c>
     </row>
@@ -3537,57 +4491,75 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D54" s="1">
-        <v>23895.45</v>
+        <v>18808.5</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.98</v>
+        <v>0.69</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.98</v>
+        <v>0.69</v>
       </c>
       <c r="G54" s="2">
-        <v>0.68</v>
+        <v>-0.71</v>
       </c>
       <c r="H54" s="2">
-        <v>-10.47</v>
+        <v>-12.15</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>25067.57</v>
+        <v>20073.77</v>
       </c>
       <c r="K54" s="1">
-        <v>23835.75</v>
+        <v>19017.36</v>
       </c>
       <c r="L54" s="1">
-        <v>24637.3</v>
+        <v>19727.89</v>
       </c>
       <c r="M54" s="3">
-        <v>-217.66</v>
+        <v>-191.96</v>
       </c>
       <c r="N54" s="3">
-        <v>-296.58</v>
+        <v>-206.66</v>
       </c>
       <c r="O54" s="3">
-        <v>-327.95</v>
+        <v>-337.73</v>
       </c>
       <c r="P54" s="3">
-        <v>-193.05</v>
+        <v>-184.66</v>
       </c>
       <c r="Q54" s="3">
-        <v>344.58</v>
+        <v>473.06</v>
       </c>
       <c r="R54" s="3">
-        <v>711.08</v>
-      </c>
-      <c r="S54" t="str">
+        <v>792.66</v>
+      </c>
+      <c r="S54" s="3">
+        <v>39.66</v>
+      </c>
+      <c r="T54" s="3">
+        <v>11.74</v>
+      </c>
+      <c r="U54" s="3">
+        <v>34.17</v>
+      </c>
+      <c r="V54" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="str">
         <v/>
       </c>
     </row>
@@ -3596,57 +4568,75 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY</v>
       </c>
       <c r="D55" s="1">
-        <v>5190.85</v>
+        <v>22753.2</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.98</v>
+        <v>0.68</v>
       </c>
       <c r="F55" s="2">
-        <v>-0.98</v>
+        <v>0.68</v>
       </c>
       <c r="G55" s="2">
-        <v>1.99</v>
+        <v>0.59</v>
       </c>
       <c r="H55" s="2">
-        <v>11.48</v>
+        <v>-12.92</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>5100.82</v>
+        <v>24101.87</v>
       </c>
       <c r="K55" s="1">
-        <v>5229.32</v>
+        <v>22748.33</v>
       </c>
       <c r="L55" s="1">
-        <v>5309.82</v>
+        <v>23370.07</v>
       </c>
       <c r="M55" s="3">
-        <v>-20.36</v>
+        <v>-157.18</v>
       </c>
       <c r="N55" s="3">
-        <v>-30.17</v>
+        <v>-209.54</v>
       </c>
       <c r="O55" s="3">
-        <v>38.14</v>
+        <v>-411.8</v>
       </c>
       <c r="P55" s="3">
-        <v>88.65</v>
+        <v>-304.9</v>
       </c>
       <c r="Q55" s="3">
-        <v>374.58</v>
+        <v>189.4</v>
       </c>
       <c r="R55" s="3">
-        <v>327.38</v>
-      </c>
-      <c r="S55" t="str">
+        <v>598.73</v>
+      </c>
+      <c r="S55" s="3">
+        <v>46.08</v>
+      </c>
+      <c r="T55" s="3">
+        <v>12.26</v>
+      </c>
+      <c r="U55" s="3">
+        <v>25.84</v>
+      </c>
+      <c r="V55" s="3">
+        <v>36.28</v>
+      </c>
+      <c r="W55" s="3">
+        <v>0</v>
+      </c>
+      <c r="X55" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="str">
         <v/>
       </c>
     </row>
@@ -3655,57 +4645,75 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C56" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D56" s="1">
-        <v>18935.75</v>
+        <v>789.7</v>
       </c>
       <c r="E56" s="2">
-        <v>-1.01</v>
+        <v>0.68</v>
       </c>
       <c r="F56" s="2">
-        <v>-1.01</v>
+        <v>0.68</v>
       </c>
       <c r="G56" s="2">
-        <v>-1.61</v>
+        <v>-6.8</v>
       </c>
       <c r="H56" s="2">
-        <v>6.9</v>
+        <v>-10.05</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>18179.82</v>
+        <v>821.28</v>
       </c>
       <c r="K56" s="1">
-        <v>19223.48</v>
+        <v>807.61</v>
       </c>
       <c r="L56" s="1">
-        <v>19680.38</v>
+        <v>859.67</v>
       </c>
       <c r="M56" s="3">
-        <v>-154.16</v>
+        <v>-17.14</v>
       </c>
       <c r="N56" s="3">
-        <v>-129.79</v>
+        <v>-15.33</v>
       </c>
       <c r="O56" s="3">
-        <v>339.32</v>
+        <v>-5.63</v>
       </c>
       <c r="P56" s="3">
-        <v>496.14</v>
+        <v>7.05</v>
       </c>
       <c r="Q56" s="3">
-        <v>892.77</v>
+        <v>0.44</v>
       </c>
       <c r="R56" s="3">
-        <v>862.73</v>
-      </c>
-      <c r="S56" t="str">
+        <v>9.67</v>
+      </c>
+      <c r="S56" s="3">
+        <v>35.19</v>
+      </c>
+      <c r="T56" s="3">
+        <v>11.87</v>
+      </c>
+      <c r="U56" s="3">
+        <v>33.79</v>
+      </c>
+      <c r="V56" s="3">
+        <v>28.59</v>
+      </c>
+      <c r="W56" s="3">
+        <v>0</v>
+      </c>
+      <c r="X56" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="str">
         <v/>
       </c>
     </row>
@@ -3714,57 +4722,75 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY200</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY200</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D57" s="1">
-        <v>13203.35</v>
+        <v>27943.6</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.01</v>
+        <v>0.64</v>
       </c>
       <c r="F57" s="2">
-        <v>-1.01</v>
+        <v>0.64</v>
       </c>
       <c r="G57" s="2">
-        <v>0.25</v>
+        <v>-7.88</v>
       </c>
       <c r="H57" s="2">
-        <v>-9.15</v>
+        <v>-8.59</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>13806.77</v>
+        <v>31373.13</v>
       </c>
       <c r="K57" s="1">
-        <v>13206.34</v>
+        <v>28844.7</v>
       </c>
       <c r="L57" s="1">
-        <v>13681.72</v>
+        <v>31303.45</v>
       </c>
       <c r="M57" s="3">
-        <v>-134.36</v>
+        <v>-870.88</v>
       </c>
       <c r="N57" s="3">
-        <v>-171.64</v>
+        <v>-732.76</v>
       </c>
       <c r="O57" s="3">
-        <v>-155.64</v>
+        <v>-704.18</v>
       </c>
       <c r="P57" s="3">
-        <v>-66.26</v>
+        <v>-91.76</v>
       </c>
       <c r="Q57" s="3">
-        <v>280.21</v>
+        <v>1935.45</v>
       </c>
       <c r="R57" s="3">
-        <v>466.43</v>
-      </c>
-      <c r="S57" t="str">
+        <v>2386.99</v>
+      </c>
+      <c r="S57" s="3">
+        <v>23.05</v>
+      </c>
+      <c r="T57" s="3">
+        <v>6.11</v>
+      </c>
+      <c r="U57" s="3">
+        <v>47.65</v>
+      </c>
+      <c r="V57" s="3">
+        <v>60.18</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="str">
         <v/>
       </c>
     </row>
@@ -3773,57 +4799,75 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D58" s="1">
-        <v>22041.6</v>
+        <v>5916</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.03</v>
+        <v>0.64</v>
       </c>
       <c r="F58" s="2">
-        <v>-1.03</v>
+        <v>0.64</v>
       </c>
       <c r="G58" s="2">
-        <v>-0.14</v>
+        <v>-5.02</v>
       </c>
       <c r="H58" s="2">
-        <v>-7.67</v>
+        <v>-7.06</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>22863.34</v>
+        <v>6740.37</v>
       </c>
       <c r="K58" s="1">
-        <v>22092.51</v>
+        <v>5993.66</v>
       </c>
       <c r="L58" s="1">
-        <v>22869.12</v>
+        <v>6280.88</v>
       </c>
       <c r="M58" s="3">
-        <v>-225.46</v>
+        <v>-106.88</v>
       </c>
       <c r="N58" s="3">
-        <v>-275.42</v>
+        <v>-97.94</v>
       </c>
       <c r="O58" s="3">
-        <v>-192.69</v>
+        <v>-221.25</v>
       </c>
       <c r="P58" s="3">
-        <v>-35.73</v>
+        <v>-162.91</v>
       </c>
       <c r="Q58" s="3">
-        <v>533.73</v>
+        <v>226.1</v>
       </c>
       <c r="R58" s="3">
-        <v>808.69</v>
-      </c>
-      <c r="S58" t="str">
+        <v>402.37</v>
+      </c>
+      <c r="S58" s="3">
+        <v>31.12</v>
+      </c>
+      <c r="T58" s="3">
+        <v>7.79</v>
+      </c>
+      <c r="U58" s="3">
+        <v>34.21</v>
+      </c>
+      <c r="V58" s="3">
+        <v>45.81</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="str">
         <v/>
       </c>
     </row>
@@ -3832,57 +4876,75 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D59" s="1">
-        <v>15678.75</v>
+        <v>26825.3</v>
       </c>
       <c r="E59" s="2">
-        <v>-1.04</v>
+        <v>0.63</v>
       </c>
       <c r="F59" s="2">
-        <v>-1.04</v>
+        <v>0.63</v>
       </c>
       <c r="G59" s="2">
-        <v>-0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H59" s="2">
-        <v>-6.98</v>
+        <v>-6.6</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>16307.73</v>
+        <v>27352.3</v>
       </c>
       <c r="K59" s="1">
-        <v>15746.43</v>
+        <v>27009.3</v>
       </c>
       <c r="L59" s="1">
-        <v>16366.58</v>
+        <v>27257.25</v>
       </c>
       <c r="M59" s="3">
-        <v>-185.36</v>
+        <v>-75.26</v>
       </c>
       <c r="N59" s="3">
-        <v>-216.84</v>
+        <v>-49.42</v>
       </c>
       <c r="O59" s="3">
-        <v>-133.4</v>
+        <v>-83.18</v>
       </c>
       <c r="P59" s="3">
-        <v>0.61</v>
+        <v>-4.83</v>
       </c>
       <c r="Q59" s="3">
-        <v>929.32</v>
+        <v>643.43</v>
       </c>
       <c r="R59" s="3">
-        <v>1181.35</v>
-      </c>
-      <c r="S59" t="str">
+        <v>874.57</v>
+      </c>
+      <c r="S59" s="3">
+        <v>44.66</v>
+      </c>
+      <c r="T59" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="U59" s="3">
+        <v>24.72</v>
+      </c>
+      <c r="V59" s="3">
+        <v>15.44</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="str">
         <v/>
       </c>
     </row>
@@ -3891,57 +4953,75 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D60" s="1">
-        <v>16767.85</v>
+        <v>11350.55</v>
       </c>
       <c r="E60" s="2">
-        <v>-1.05</v>
+        <v>0.62</v>
       </c>
       <c r="F60" s="2">
-        <v>-1.05</v>
+        <v>0.62</v>
       </c>
       <c r="G60" s="2">
-        <v>-1.53</v>
+        <v>1.84</v>
       </c>
       <c r="H60" s="2">
-        <v>-2.82</v>
+        <v>-14.5</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>17231.35</v>
+        <v>12162.16</v>
       </c>
       <c r="K60" s="1">
-        <v>16936.71</v>
+        <v>11323.59</v>
       </c>
       <c r="L60" s="1">
-        <v>17751.15</v>
+        <v>11523.99</v>
       </c>
       <c r="M60" s="3">
-        <v>-261.77</v>
+        <v>-37.74</v>
       </c>
       <c r="N60" s="3">
-        <v>-278.24</v>
+        <v>-72.48</v>
       </c>
       <c r="O60" s="3">
-        <v>-33.85</v>
+        <v>-261.72</v>
       </c>
       <c r="P60" s="3">
-        <v>164.81</v>
+        <v>-241.43</v>
       </c>
       <c r="Q60" s="3">
-        <v>915.94</v>
+        <v>-128.05</v>
       </c>
       <c r="R60" s="3">
-        <v>1051.43</v>
-      </c>
-      <c r="S60" t="str">
+        <v>114.83</v>
+      </c>
+      <c r="S60" s="3">
+        <v>49.45</v>
+      </c>
+      <c r="T60" s="3">
+        <v>14.88</v>
+      </c>
+      <c r="U60" s="3">
+        <v>25.5</v>
+      </c>
+      <c r="V60" s="3">
+        <v>28.85</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="str">
         <v/>
       </c>
     </row>
@@ -3950,57 +5030,75 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D61" s="1">
-        <v>15656.8</v>
+        <v>4676.75</v>
       </c>
       <c r="E61" s="2">
-        <v>-1.05</v>
+        <v>0.62</v>
       </c>
       <c r="F61" s="2">
-        <v>-1.05</v>
+        <v>0.62</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.59</v>
+        <v>-0.15</v>
       </c>
       <c r="H61" s="2">
-        <v>-5.02</v>
+        <v>-9.74</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>16029.65</v>
+        <v>4910.04</v>
       </c>
       <c r="K61" s="1">
-        <v>15736.72</v>
+        <v>4693.97</v>
       </c>
       <c r="L61" s="1">
-        <v>16277.41</v>
+        <v>4849.39</v>
       </c>
       <c r="M61" s="3">
-        <v>-162.34</v>
+        <v>-40.76</v>
       </c>
       <c r="N61" s="3">
-        <v>-186.97</v>
+        <v>-50.18</v>
       </c>
       <c r="O61" s="3">
-        <v>-59.62</v>
+        <v>-60.85</v>
       </c>
       <c r="P61" s="3">
-        <v>64.71</v>
+        <v>-26.54</v>
       </c>
       <c r="Q61" s="3">
-        <v>933.56</v>
+        <v>218.68</v>
       </c>
       <c r="R61" s="3">
-        <v>1151.4</v>
-      </c>
-      <c r="S61" t="str">
+        <v>299.16</v>
+      </c>
+      <c r="S61" s="3">
+        <v>43.2</v>
+      </c>
+      <c r="T61" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="U61" s="3">
+        <v>30.16</v>
+      </c>
+      <c r="V61" s="3">
+        <v>37.65</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="str">
         <v/>
       </c>
     </row>
@@ -4009,57 +5107,75 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D62" s="1">
-        <v>12469.05</v>
+        <v>3775.2</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.05</v>
+        <v>0.59</v>
       </c>
       <c r="F62" s="2">
-        <v>-1.05</v>
+        <v>0.59</v>
       </c>
       <c r="G62" s="2">
-        <v>-0.29</v>
+        <v>-0.19</v>
       </c>
       <c r="H62" s="2">
-        <v>-6.9</v>
+        <v>-13.28</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>12872.91</v>
+        <v>4028.78</v>
       </c>
       <c r="K62" s="1">
-        <v>12505.65</v>
+        <v>3786.82</v>
       </c>
       <c r="L62" s="1">
-        <v>12934.02</v>
+        <v>3911.18</v>
       </c>
       <c r="M62" s="3">
-        <v>-125.26</v>
+        <v>-34.04</v>
       </c>
       <c r="N62" s="3">
-        <v>-150.83</v>
+        <v>-41.22</v>
       </c>
       <c r="O62" s="3">
-        <v>-86.46</v>
+        <v>-73.13</v>
       </c>
       <c r="P62" s="3">
-        <v>3.2</v>
+        <v>-49.11</v>
       </c>
       <c r="Q62" s="3">
-        <v>640.24</v>
+        <v>124.85</v>
       </c>
       <c r="R62" s="3">
-        <v>828.13</v>
-      </c>
-      <c r="S62" t="str">
+        <v>206.49</v>
+      </c>
+      <c r="S62" s="3">
+        <v>43.3</v>
+      </c>
+      <c r="T62" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="U62" s="3">
+        <v>28.63</v>
+      </c>
+      <c r="V62" s="3">
+        <v>37.61</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="str">
         <v/>
       </c>
     </row>
@@ -4068,57 +5184,75 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D63" s="1">
-        <v>10938.6</v>
+        <v>18670.3</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.05</v>
+        <v>0.58</v>
       </c>
       <c r="F63" s="2">
-        <v>-1.05</v>
+        <v>0.58</v>
       </c>
       <c r="G63" s="2">
-        <v>-1.21</v>
+        <v>-0.61</v>
       </c>
       <c r="H63" s="2">
-        <v>-10.99</v>
+        <v>-11.64</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>11510.65</v>
+        <v>19842.75</v>
       </c>
       <c r="K63" s="1">
-        <v>10982.36</v>
+        <v>18702.31</v>
       </c>
       <c r="L63" s="1">
-        <v>11533.73</v>
+        <v>19424.04</v>
       </c>
       <c r="M63" s="3">
-        <v>-165.76</v>
+        <v>-204.94</v>
       </c>
       <c r="N63" s="3">
-        <v>-187.83</v>
+        <v>-242.65</v>
       </c>
       <c r="O63" s="3">
-        <v>-142.76</v>
+        <v>-333.97</v>
       </c>
       <c r="P63" s="3">
-        <v>-39.79</v>
+        <v>-184.77</v>
       </c>
       <c r="Q63" s="3">
-        <v>225.56</v>
+        <v>754.66</v>
       </c>
       <c r="R63" s="3">
-        <v>395.78</v>
-      </c>
-      <c r="S63" t="str">
+        <v>1110.75</v>
+      </c>
+      <c r="S63" s="3">
+        <v>41.44</v>
+      </c>
+      <c r="T63" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="U63" s="3">
+        <v>26.16</v>
+      </c>
+      <c r="V63" s="3">
+        <v>48.96</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="str">
         <v/>
       </c>
     </row>
@@ -4127,57 +5261,75 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C64" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D64" s="1">
-        <v>58487.95</v>
+        <v>5539.2</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.09</v>
+        <v>0.52</v>
       </c>
       <c r="F64" s="2">
-        <v>-1.09</v>
+        <v>0.52</v>
       </c>
       <c r="G64" s="2">
-        <v>-1.42</v>
+        <v>1.22</v>
       </c>
       <c r="H64" s="2">
-        <v>-3.3</v>
+        <v>-13.25</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>60345.06</v>
+        <v>5944.58</v>
       </c>
       <c r="K64" s="1">
-        <v>59144.52</v>
+        <v>5542.79</v>
       </c>
       <c r="L64" s="1">
-        <v>61831.43</v>
+        <v>5669.49</v>
       </c>
       <c r="M64" s="3">
-        <v>-847.38</v>
+        <v>-23.96</v>
       </c>
       <c r="N64" s="3">
-        <v>-899.29</v>
+        <v>-44.27</v>
       </c>
       <c r="O64" s="3">
-        <v>-224.86</v>
+        <v>-121.86</v>
       </c>
       <c r="P64" s="3">
-        <v>439.1</v>
+        <v>-101.53</v>
       </c>
       <c r="Q64" s="3">
-        <v>2942.36</v>
+        <v>24.07</v>
       </c>
       <c r="R64" s="3">
-        <v>3494.39</v>
-      </c>
-      <c r="S64" t="str">
+        <v>139.3</v>
+      </c>
+      <c r="S64" s="3">
+        <v>47.42</v>
+      </c>
+      <c r="T64" s="3">
+        <v>15.54</v>
+      </c>
+      <c r="U64" s="3">
+        <v>28.34</v>
+      </c>
+      <c r="V64" s="3">
+        <v>34.18</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="str">
         <v/>
       </c>
     </row>
@@ -4186,57 +5338,75 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D65" s="1">
-        <v>21499.3</v>
+        <v>24970.75</v>
       </c>
       <c r="E65" s="2">
-        <v>-1.09</v>
+        <v>0.44</v>
       </c>
       <c r="F65" s="2">
-        <v>-1.09</v>
+        <v>0.44</v>
       </c>
       <c r="G65" s="2">
-        <v>-1.68</v>
+        <v>-5.03</v>
       </c>
       <c r="H65" s="2">
-        <v>-3.49</v>
+        <v>-11.42</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>22194.72</v>
+        <v>26894.25</v>
       </c>
       <c r="K65" s="1">
-        <v>21742.54</v>
+        <v>25225.58</v>
       </c>
       <c r="L65" s="1">
-        <v>22724.19</v>
+        <v>27080.76</v>
       </c>
       <c r="M65" s="3">
-        <v>-313.55</v>
+        <v>-540.62</v>
       </c>
       <c r="N65" s="3">
-        <v>-328.14</v>
+        <v>-588.96</v>
       </c>
       <c r="O65" s="3">
-        <v>-80.46</v>
+        <v>-404.95</v>
       </c>
       <c r="P65" s="3">
-        <v>162.72</v>
+        <v>-8.1</v>
       </c>
       <c r="Q65" s="3">
-        <v>1726.57</v>
+        <v>1457.85</v>
       </c>
       <c r="R65" s="3">
-        <v>2031.93</v>
-      </c>
-      <c r="S65" t="str">
+        <v>1807.07</v>
+      </c>
+      <c r="S65" s="3">
+        <v>36.26</v>
+      </c>
+      <c r="T65" s="3">
+        <v>9.49</v>
+      </c>
+      <c r="U65" s="3">
+        <v>33.55</v>
+      </c>
+      <c r="V65" s="3">
+        <v>55.32</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="str">
         <v/>
       </c>
     </row>
@@ -4245,57 +5415,75 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D66" s="1">
-        <v>4737.1</v>
+        <v>23921.55</v>
       </c>
       <c r="E66" s="2">
-        <v>-1.09</v>
+        <v>0.4</v>
       </c>
       <c r="F66" s="2">
-        <v>-1.09</v>
+        <v>0.4</v>
       </c>
       <c r="G66" s="2">
-        <v>1.14</v>
+        <v>-8.87</v>
       </c>
       <c r="H66" s="2">
-        <v>-8.57</v>
+        <v>6.1</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>4919.82</v>
+        <v>23631.39</v>
       </c>
       <c r="K66" s="1">
-        <v>4714.02</v>
+        <v>24850.41</v>
       </c>
       <c r="L66" s="1">
-        <v>4884.75</v>
+        <v>26031.33</v>
       </c>
       <c r="M66" s="3">
-        <v>-43.77</v>
+        <v>-499.1</v>
       </c>
       <c r="N66" s="3">
-        <v>-63.54</v>
+        <v>-280.09</v>
       </c>
       <c r="O66" s="3">
-        <v>-47.12</v>
+        <v>396.37</v>
       </c>
       <c r="P66" s="3">
-        <v>-16.54</v>
+        <v>757.8</v>
       </c>
       <c r="Q66" s="3">
-        <v>223.49</v>
+        <v>2252.91</v>
       </c>
       <c r="R66" s="3">
-        <v>300.13</v>
-      </c>
-      <c r="S66" t="str">
+        <v>2343.28</v>
+      </c>
+      <c r="S66" s="3">
+        <v>27.64</v>
+      </c>
+      <c r="T66" s="3">
+        <v>9.66</v>
+      </c>
+      <c r="U66" s="3">
+        <v>46.98</v>
+      </c>
+      <c r="V66" s="3">
+        <v>35.75</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="str">
         <v/>
       </c>
     </row>
@@ -4304,57 +5492,75 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D67" s="1">
-        <v>22888.95</v>
+        <v>10927.15</v>
       </c>
       <c r="E67" s="2">
-        <v>-1.11</v>
+        <v>0.35</v>
       </c>
       <c r="F67" s="2">
-        <v>-1.11</v>
+        <v>0.35</v>
       </c>
       <c r="G67" s="2">
-        <v>1.19</v>
+        <v>3.68</v>
       </c>
       <c r="H67" s="2">
-        <v>-12.4</v>
+        <v>-12.47</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>24168.4</v>
+        <v>11208.45</v>
       </c>
       <c r="K67" s="1">
-        <v>22798.07</v>
+        <v>10832.41</v>
       </c>
       <c r="L67" s="1">
-        <v>23514.27</v>
+        <v>11051.88</v>
       </c>
       <c r="M67" s="3">
-        <v>-185.04</v>
+        <v>-10.42</v>
       </c>
       <c r="N67" s="3">
-        <v>-273.79</v>
+        <v>-81.24</v>
       </c>
       <c r="O67" s="3">
-        <v>-378</v>
+        <v>-108.74</v>
       </c>
       <c r="P67" s="3">
-        <v>-273.57</v>
+        <v>-82.58</v>
       </c>
       <c r="Q67" s="3">
-        <v>200.23</v>
+        <v>34.48</v>
       </c>
       <c r="R67" s="3">
-        <v>600.9</v>
-      </c>
-      <c r="S67" t="str">
+        <v>177.14</v>
+      </c>
+      <c r="S67" s="3">
+        <v>54.39</v>
+      </c>
+      <c r="T67" s="3">
+        <v>17.61</v>
+      </c>
+      <c r="U67" s="3">
+        <v>21.56</v>
+      </c>
+      <c r="V67" s="3">
+        <v>30.83</v>
+      </c>
+      <c r="W67" s="3">
+        <v>0</v>
+      </c>
+      <c r="X67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="str">
         <v/>
       </c>
     </row>
@@ -4363,57 +5569,75 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D68" s="1">
-        <v>20045.25</v>
+        <v>8093.8</v>
       </c>
       <c r="E68" s="2">
-        <v>-1.11</v>
+        <v>0.29</v>
       </c>
       <c r="F68" s="2">
-        <v>-1.11</v>
+        <v>0.29</v>
       </c>
       <c r="G68" s="2">
-        <v>-1.81</v>
+        <v>0.97</v>
       </c>
       <c r="H68" s="2">
-        <v>-0.85</v>
+        <v>-5.15</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>20269.45</v>
+        <v>8569.56</v>
       </c>
       <c r="K68" s="1">
-        <v>20294.36</v>
+        <v>8141.52</v>
       </c>
       <c r="L68" s="1">
-        <v>21071.25</v>
+        <v>8330.58</v>
       </c>
       <c r="M68" s="3">
-        <v>-252.22</v>
+        <v>-37.38</v>
       </c>
       <c r="N68" s="3">
-        <v>-253.81</v>
+        <v>-57.31</v>
       </c>
       <c r="O68" s="3">
-        <v>46.95</v>
+        <v>-96.89</v>
       </c>
       <c r="P68" s="3">
-        <v>255.26</v>
+        <v>-45.5</v>
       </c>
       <c r="Q68" s="3">
-        <v>1600.32</v>
+        <v>562.79</v>
       </c>
       <c r="R68" s="3">
-        <v>1827.81</v>
-      </c>
-      <c r="S68" t="str">
+        <v>682.88</v>
+      </c>
+      <c r="S68" s="3">
+        <v>45.74</v>
+      </c>
+      <c r="T68" s="3">
+        <v>18.98</v>
+      </c>
+      <c r="U68" s="3">
+        <v>24.78</v>
+      </c>
+      <c r="V68" s="3">
+        <v>18.2</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="str">
         <v/>
       </c>
     </row>
@@ -4422,57 +5646,75 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D69" s="1">
-        <v>13565.15</v>
+        <v>42800.75</v>
       </c>
       <c r="E69" s="2">
-        <v>-1.11</v>
+        <v>0.28</v>
       </c>
       <c r="F69" s="2">
-        <v>-1.11</v>
+        <v>0.28</v>
       </c>
       <c r="G69" s="2">
-        <v>-1.21</v>
+        <v>-3.84</v>
       </c>
       <c r="H69" s="2">
-        <v>-1.54</v>
+        <v>-22.85</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>14003.41</v>
+        <v>48852.27</v>
       </c>
       <c r="K69" s="1">
-        <v>13704.6</v>
+        <v>43725.04</v>
       </c>
       <c r="L69" s="1">
-        <v>14407.94</v>
+        <v>45647.82</v>
       </c>
       <c r="M69" s="3">
-        <v>-218.84</v>
+        <v>-712.46</v>
       </c>
       <c r="N69" s="3">
-        <v>-240.63</v>
+        <v>-579.61</v>
       </c>
       <c r="O69" s="3">
-        <v>-53.14</v>
+        <v>-1797.49</v>
       </c>
       <c r="P69" s="3">
-        <v>130.65</v>
+        <v>-1448.69</v>
       </c>
       <c r="Q69" s="3">
-        <v>887.23</v>
+        <v>-2210.25</v>
       </c>
       <c r="R69" s="3">
-        <v>1004.13</v>
-      </c>
-      <c r="S69" t="str">
+        <v>-974.87</v>
+      </c>
+      <c r="S69" s="3">
+        <v>34.83</v>
+      </c>
+      <c r="T69" s="3">
+        <v>10.75</v>
+      </c>
+      <c r="U69" s="3">
+        <v>34.44</v>
+      </c>
+      <c r="V69" s="3">
+        <v>39.08</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="str">
         <v/>
       </c>
     </row>
@@ -4481,57 +5723,75 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D70" s="1">
-        <v>35840.55</v>
+        <v>24454.35</v>
       </c>
       <c r="E70" s="2">
-        <v>-1.12</v>
+        <v>0.21</v>
       </c>
       <c r="F70" s="2">
-        <v>-1.12</v>
+        <v>0.21</v>
       </c>
       <c r="G70" s="2">
-        <v>-2.15</v>
+        <v>-0.79</v>
       </c>
       <c r="H70" s="2">
-        <v>-2.49</v>
+        <v>-11.44</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>37126.93</v>
+        <v>26191.05</v>
       </c>
       <c r="K70" s="1">
-        <v>36345.95</v>
+        <v>24770.06</v>
       </c>
       <c r="L70" s="1">
-        <v>38605.84</v>
+        <v>25444.57</v>
       </c>
       <c r="M70" s="3">
-        <v>-700.92</v>
+        <v>-210.19</v>
       </c>
       <c r="N70" s="3">
-        <v>-737.05</v>
+        <v>-192.26</v>
       </c>
       <c r="O70" s="3">
-        <v>-143</v>
+        <v>-424.2</v>
       </c>
       <c r="P70" s="3">
-        <v>326.12</v>
+        <v>-266.41</v>
       </c>
       <c r="Q70" s="3">
-        <v>685.97</v>
+        <v>632.02</v>
       </c>
       <c r="R70" s="3">
-        <v>949.36</v>
-      </c>
-      <c r="S70" t="str">
+        <v>1077.96</v>
+      </c>
+      <c r="S70" s="3">
+        <v>38.73</v>
+      </c>
+      <c r="T70" s="3">
+        <v>12.19</v>
+      </c>
+      <c r="U70" s="3">
+        <v>28.27</v>
+      </c>
+      <c r="V70" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="str">
         <v/>
       </c>
     </row>
@@ -4540,57 +5800,75 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D71" s="1">
-        <v>17435.15</v>
+        <v>26242.55</v>
       </c>
       <c r="E71" s="2">
-        <v>-1.15</v>
+        <v>0.18</v>
       </c>
       <c r="F71" s="2">
-        <v>-1.15</v>
+        <v>0.18</v>
       </c>
       <c r="G71" s="2">
-        <v>-2.04</v>
+        <v>-1.18</v>
       </c>
       <c r="H71" s="2">
-        <v>4.5</v>
+        <v>-13.04</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>16946.17</v>
+        <v>28507.78</v>
       </c>
       <c r="K71" s="1">
-        <v>17687.1</v>
+        <v>26611.8</v>
       </c>
       <c r="L71" s="1">
-        <v>18138.87</v>
+        <v>27503.64</v>
       </c>
       <c r="M71" s="3">
-        <v>-154.43</v>
+        <v>-280.13</v>
       </c>
       <c r="N71" s="3">
-        <v>-136.52</v>
+        <v>-266.79</v>
       </c>
       <c r="O71" s="3">
-        <v>238.04</v>
+        <v>-562.75</v>
       </c>
       <c r="P71" s="3">
-        <v>389.47</v>
+        <v>-353.46</v>
       </c>
       <c r="Q71" s="3">
-        <v>1339.23</v>
+        <v>1285.69</v>
       </c>
       <c r="R71" s="3">
-        <v>1435.09</v>
-      </c>
-      <c r="S71" t="str">
+        <v>1895.05</v>
+      </c>
+      <c r="S71" s="3">
+        <v>37.01</v>
+      </c>
+      <c r="T71" s="3">
+        <v>11.59</v>
+      </c>
+      <c r="U71" s="3">
+        <v>29.99</v>
+      </c>
+      <c r="V71" s="3">
+        <v>29.61</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="str">
         <v/>
       </c>
     </row>
@@ -4599,57 +5877,75 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D72" s="1">
-        <v>7373.5</v>
+        <v>54366.7</v>
       </c>
       <c r="E72" s="2">
-        <v>-1.15</v>
+        <v>0.15</v>
       </c>
       <c r="F72" s="2">
-        <v>-1.15</v>
+        <v>0.15</v>
       </c>
       <c r="G72" s="2">
-        <v>4.2</v>
+        <v>-0.49</v>
       </c>
       <c r="H72" s="2">
-        <v>-2.5</v>
+        <v>-8.75</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>7336.18</v>
+        <v>56816.25</v>
       </c>
       <c r="K72" s="1">
-        <v>7277.83</v>
+        <v>54943.8</v>
       </c>
       <c r="L72" s="1">
-        <v>7418.47</v>
+        <v>56189.32</v>
       </c>
       <c r="M72" s="3">
-        <v>-14.64</v>
+        <v>-363.92</v>
       </c>
       <c r="N72" s="3">
-        <v>-58.79</v>
+        <v>-353.9</v>
       </c>
       <c r="O72" s="3">
-        <v>2.99</v>
+        <v>-495.53</v>
       </c>
       <c r="P72" s="3">
-        <v>32.07</v>
+        <v>-186.53</v>
       </c>
       <c r="Q72" s="3">
-        <v>473.87</v>
+        <v>1616.41</v>
       </c>
       <c r="R72" s="3">
-        <v>552.98</v>
-      </c>
-      <c r="S72" t="str">
+        <v>2278.86</v>
+      </c>
+      <c r="S72" s="3">
+        <v>38.74</v>
+      </c>
+      <c r="T72" s="3">
+        <v>11.02</v>
+      </c>
+      <c r="U72" s="3">
+        <v>26.88</v>
+      </c>
+      <c r="V72" s="3">
+        <v>24.35</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="str">
         <v/>
       </c>
     </row>
@@ -4658,57 +5954,75 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D73" s="1">
-        <v>22698.65</v>
+        <v>26353.4</v>
       </c>
       <c r="E73" s="2">
-        <v>-1.16</v>
+        <v>0.11</v>
       </c>
       <c r="F73" s="2">
-        <v>-1.16</v>
+        <v>0.11</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.3</v>
-      </c>
-      <c r="H73" s="2">
-        <v>-5.65</v>
+        <v>-7.09</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
-      <c r="J73" s="1">
-        <v>23508.76</v>
+      <c r="J73" t="str">
+        <v/>
       </c>
       <c r="K73" s="1">
-        <v>22906.09</v>
+        <v>27374.94</v>
       </c>
       <c r="L73" s="1">
-        <v>23833.06</v>
+        <v>29160.65</v>
       </c>
       <c r="M73" s="3">
-        <v>-257.13</v>
+        <v>-647.18</v>
       </c>
       <c r="N73" s="3">
-        <v>-301.12</v>
+        <v>-489.44</v>
       </c>
       <c r="O73" s="3">
-        <v>-179.1</v>
+        <v>-422.68</v>
       </c>
       <c r="P73" s="3">
-        <v>36.28</v>
+        <v>42.14</v>
       </c>
       <c r="Q73" s="3">
-        <v>1041.01</v>
+        <v>158.3</v>
       </c>
       <c r="R73" s="3">
-        <v>1363.04</v>
-      </c>
-      <c r="S73" t="str">
+        <v>172.94</v>
+      </c>
+      <c r="S73" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="T73" s="3">
+        <v>10.48</v>
+      </c>
+      <c r="U73" s="3">
+        <v>45.17</v>
+      </c>
+      <c r="V73" s="3">
+        <v>40.96</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="str">
         <v/>
       </c>
     </row>
@@ -4717,57 +6031,75 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D74" s="1">
-        <v>19244.1</v>
+        <v>1300.92</v>
       </c>
       <c r="E74" s="2">
-        <v>-1.16</v>
+        <v>0.06</v>
       </c>
       <c r="F74" s="2">
-        <v>-1.16</v>
+        <v>0.06</v>
       </c>
       <c r="G74" s="2">
-        <v>1.59</v>
+        <v>-1.11</v>
       </c>
       <c r="H74" s="2">
-        <v>-10.12</v>
+        <v>0.21</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>20122.6</v>
+        <v>1308.02</v>
       </c>
       <c r="K74" s="1">
-        <v>19201.68</v>
+        <v>1306.92</v>
       </c>
       <c r="L74" s="1">
-        <v>19894.51</v>
+        <v>1320.54</v>
       </c>
       <c r="M74" s="3">
-        <v>-157.5</v>
+        <v>-5.03</v>
       </c>
       <c r="N74" s="3">
-        <v>-252.48</v>
+        <v>-4.04</v>
       </c>
       <c r="O74" s="3">
-        <v>-258.22</v>
+        <v>0.37</v>
       </c>
       <c r="P74" s="3">
-        <v>-137.4</v>
+        <v>4.56</v>
       </c>
       <c r="Q74" s="3">
-        <v>507.8</v>
+        <v>23.55</v>
       </c>
       <c r="R74" s="3">
-        <v>799.61</v>
-      </c>
-      <c r="S74" t="str">
+        <v>24.12</v>
+      </c>
+      <c r="S74" s="3">
+        <v>19.42</v>
+      </c>
+      <c r="T74" s="3">
+        <v>19.95</v>
+      </c>
+      <c r="U74" s="3">
+        <v>77.59</v>
+      </c>
+      <c r="V74" s="3">
+        <v>40.86</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="str">
         <v/>
       </c>
     </row>
@@ -4776,57 +6108,75 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C75" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D75" s="1">
-        <v>816.05</v>
+        <v>3453.38</v>
       </c>
       <c r="E75" s="2">
-        <v>-1.2</v>
+        <v>0.05</v>
       </c>
       <c r="F75" s="2">
-        <v>-1.2</v>
+        <v>0.05</v>
       </c>
       <c r="G75" s="2">
-        <v>-3.69</v>
+        <v>-1.94</v>
       </c>
       <c r="H75" s="2">
-        <v>-7.05</v>
+        <v>-1.13</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>822.91</v>
+        <v>3495.08</v>
       </c>
       <c r="K75" s="1">
-        <v>824.12</v>
+        <v>3472.6</v>
       </c>
       <c r="L75" s="1">
-        <v>867.25</v>
+        <v>3529.21</v>
       </c>
       <c r="M75" s="3">
-        <v>-13.57</v>
+        <v>-20.41</v>
       </c>
       <c r="N75" s="3">
-        <v>-14.54</v>
+        <v>-17.21</v>
       </c>
       <c r="O75" s="3">
-        <v>0.89</v>
+        <v>-3.59</v>
       </c>
       <c r="P75" s="3">
-        <v>10.72</v>
+        <v>11.41</v>
       </c>
       <c r="Q75" s="3">
-        <v>2.54</v>
+        <v>117.61</v>
       </c>
       <c r="R75" s="3">
-        <v>10.09</v>
-      </c>
-      <c r="S75" t="str">
+        <v>141.66</v>
+      </c>
+      <c r="S75" s="3">
+        <v>31.33</v>
+      </c>
+      <c r="T75" s="3">
+        <v>14.87</v>
+      </c>
+      <c r="U75" s="3">
+        <v>38.02</v>
+      </c>
+      <c r="V75" s="3">
+        <v>32.21</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="str">
         <v/>
       </c>
     </row>
@@ -4835,57 +6185,75 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D76" s="1">
-        <v>11392.1</v>
+        <v>1596.65</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.22</v>
+        <v>0.03</v>
       </c>
       <c r="F76" s="2">
-        <v>-1.22</v>
+        <v>0.03</v>
       </c>
       <c r="G76" s="2">
-        <v>2.21</v>
+        <v>-0.64</v>
       </c>
       <c r="H76" s="2">
-        <v>-14.19</v>
+        <v>1.9</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>12199.92</v>
+        <v>1586.97</v>
       </c>
       <c r="K76" s="1">
-        <v>11310.44</v>
+        <v>1600.87</v>
       </c>
       <c r="L76" s="1">
-        <v>11584.13</v>
+        <v>1608.2</v>
       </c>
       <c r="M76" s="3">
-        <v>-59.98</v>
+        <v>-2.96</v>
       </c>
       <c r="N76" s="3">
-        <v>-115.63</v>
+        <v>-2.04</v>
       </c>
       <c r="O76" s="3">
-        <v>-258.76</v>
+        <v>5.43</v>
       </c>
       <c r="P76" s="3">
-        <v>-234.58</v>
+        <v>8.52</v>
       </c>
       <c r="Q76" s="3">
-        <v>-124.74</v>
+        <v>34.52</v>
       </c>
       <c r="R76" s="3">
-        <v>115.49</v>
-      </c>
-      <c r="S76" t="str">
+        <v>33.05</v>
+      </c>
+      <c r="S76" s="3">
+        <v>25.47</v>
+      </c>
+      <c r="T76" s="3">
+        <v>18.9</v>
+      </c>
+      <c r="U76" s="3">
+        <v>68.23</v>
+      </c>
+      <c r="V76" s="3">
+        <v>30.23</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="str">
         <v/>
       </c>
     </row>
@@ -4894,57 +6262,75 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C77" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D77" s="1">
-        <v>30099.85</v>
+        <v>1440.84</v>
       </c>
       <c r="E77" s="2">
-        <v>-1.25</v>
+        <v>0.03</v>
       </c>
       <c r="F77" s="2">
-        <v>-1.25</v>
+        <v>0.03</v>
       </c>
       <c r="G77" s="2">
-        <v>3.74</v>
+        <v>-0.9</v>
       </c>
       <c r="H77" s="2">
-        <v>-10.57</v>
+        <v>1.13</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>30995.16</v>
+        <v>1440.95</v>
       </c>
       <c r="K77" s="1">
-        <v>29659.55</v>
+        <v>1446.27</v>
       </c>
       <c r="L77" s="1">
-        <v>30157.43</v>
+        <v>1457.26</v>
       </c>
       <c r="M77" s="3">
-        <v>-65.9</v>
+        <v>-4.15</v>
       </c>
       <c r="N77" s="3">
-        <v>-249.18</v>
+        <v>-3.2</v>
       </c>
       <c r="O77" s="3">
-        <v>-346.4</v>
+        <v>2.54</v>
       </c>
       <c r="P77" s="3">
-        <v>-314.78</v>
+        <v>6.3</v>
       </c>
       <c r="Q77" s="3">
-        <v>495.29</v>
+        <v>28.76</v>
       </c>
       <c r="R77" s="3">
-        <v>993.55</v>
-      </c>
-      <c r="S77" t="str">
+        <v>28.47</v>
+      </c>
+      <c r="S77" s="3">
+        <v>20.25</v>
+      </c>
+      <c r="T77" s="3">
+        <v>17.93</v>
+      </c>
+      <c r="U77" s="3">
+        <v>73.95</v>
+      </c>
+      <c r="V77" s="3">
+        <v>36.84</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="str">
         <v/>
       </c>
     </row>
@@ -4953,57 +6339,75 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D78" s="1">
-        <v>15866</v>
+        <v>3277.41</v>
       </c>
       <c r="E78" s="2">
-        <v>-1.27</v>
+        <v>0.02</v>
       </c>
       <c r="F78" s="2">
-        <v>-1.27</v>
+        <v>0.02</v>
       </c>
       <c r="G78" s="2">
-        <v>-2.6</v>
+        <v>-0.94</v>
       </c>
       <c r="H78" s="2">
-        <v>-0.86</v>
+        <v>1.7</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>16134.51</v>
+        <v>3280.69</v>
       </c>
       <c r="K78" s="1">
-        <v>16147.79</v>
+        <v>3283.08</v>
       </c>
       <c r="L78" s="1">
-        <v>16888.42</v>
+        <v>3318.47</v>
       </c>
       <c r="M78" s="3">
-        <v>-238.03</v>
+        <v>-11.86</v>
       </c>
       <c r="N78" s="3">
-        <v>-235.4</v>
+        <v>-11.42</v>
       </c>
       <c r="O78" s="3">
-        <v>43.53</v>
+        <v>4.88</v>
       </c>
       <c r="P78" s="3">
-        <v>234.52</v>
+        <v>15.37</v>
       </c>
       <c r="Q78" s="3">
-        <v>1565.9</v>
+        <v>139.52</v>
       </c>
       <c r="R78" s="3">
-        <v>1751.51</v>
-      </c>
-      <c r="S78" t="str">
+        <v>155.41</v>
+      </c>
+      <c r="S78" s="3">
+        <v>25.86</v>
+      </c>
+      <c r="T78" s="3">
+        <v>12.19</v>
+      </c>
+      <c r="U78" s="3">
+        <v>44.27</v>
+      </c>
+      <c r="V78" s="3">
+        <v>49.53</v>
+      </c>
+      <c r="W78" s="3">
+        <v>0</v>
+      </c>
+      <c r="X78" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="str">
         <v/>
       </c>
     </row>
@@ -5012,57 +6416,75 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C79" t="str">
-        <v>CNXIT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D79" s="1">
-        <v>31516.3</v>
+        <v>2966.26</v>
       </c>
       <c r="E79" s="2">
-        <v>-1.28</v>
+        <v>0.02</v>
       </c>
       <c r="F79" s="2">
-        <v>-1.28</v>
+        <v>0.02</v>
       </c>
       <c r="G79" s="2">
-        <v>13.76</v>
+        <v>-1.58</v>
       </c>
       <c r="H79" s="2">
-        <v>-16.81</v>
+        <v>-0.02</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>30903.39</v>
+        <v>3001.33</v>
       </c>
       <c r="K79" s="1">
-        <v>29999.76</v>
+        <v>2976.7</v>
       </c>
       <c r="L79" s="1">
-        <v>29809.61</v>
+        <v>3023.32</v>
       </c>
       <c r="M79" s="3">
-        <v>395.38</v>
+        <v>-16.34</v>
       </c>
       <c r="N79" s="3">
-        <v>-87.44</v>
+        <v>-15.03</v>
       </c>
       <c r="O79" s="3">
-        <v>-195.07</v>
+        <v>-3.56</v>
       </c>
       <c r="P79" s="3">
-        <v>-527.2</v>
+        <v>8.36</v>
       </c>
       <c r="Q79" s="3">
-        <v>-1699.24</v>
+        <v>114.43</v>
       </c>
       <c r="R79" s="3">
-        <v>-1155.4</v>
-      </c>
-      <c r="S79" t="str">
+        <v>132.76</v>
+      </c>
+      <c r="S79" s="3">
+        <v>25.13</v>
+      </c>
+      <c r="T79" s="3">
+        <v>12.27</v>
+      </c>
+      <c r="U79" s="3">
+        <v>44.07</v>
+      </c>
+      <c r="V79" s="3">
+        <v>51.29</v>
+      </c>
+      <c r="W79" s="3">
+        <v>0</v>
+      </c>
+      <c r="X79" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="str">
         <v/>
       </c>
     </row>
@@ -5071,57 +6493,75 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D80" s="1">
-        <v>8336.65</v>
+        <v>3057.5</v>
       </c>
       <c r="E80" s="2">
-        <v>-1.32</v>
+        <v>0.01</v>
       </c>
       <c r="F80" s="2">
-        <v>-1.32</v>
+        <v>0.01</v>
       </c>
       <c r="G80" s="2">
-        <v>3.21</v>
+        <v>-1.51</v>
       </c>
       <c r="H80" s="2">
-        <v>-17</v>
+        <v>0.17</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>8788.93</v>
+        <v>3085.98</v>
       </c>
       <c r="K80" s="1">
-        <v>8269.57</v>
+        <v>3068.62</v>
       </c>
       <c r="L80" s="1">
-        <v>8415.39</v>
+        <v>3115.23</v>
       </c>
       <c r="M80" s="3">
-        <v>-20.17</v>
+        <v>-16.22</v>
       </c>
       <c r="N80" s="3">
-        <v>-63.71</v>
+        <v>-14.89</v>
       </c>
       <c r="O80" s="3">
-        <v>-157.19</v>
+        <v>-1.47</v>
       </c>
       <c r="P80" s="3">
-        <v>-157.96</v>
+        <v>10.82</v>
       </c>
       <c r="Q80" s="3">
-        <v>-302.52</v>
+        <v>118.24</v>
       </c>
       <c r="R80" s="3">
-        <v>-191.83</v>
-      </c>
-      <c r="S80" t="str">
+        <v>136.5</v>
+      </c>
+      <c r="S80" s="3">
+        <v>26.77</v>
+      </c>
+      <c r="T80" s="3">
+        <v>11.11</v>
+      </c>
+      <c r="U80" s="3">
+        <v>43.25</v>
+      </c>
+      <c r="V80" s="3">
+        <v>49.09</v>
+      </c>
+      <c r="W80" s="3">
+        <v>0</v>
+      </c>
+      <c r="X80" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="str">
         <v/>
       </c>
     </row>
@@ -5130,57 +6570,75 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D81" s="1">
-        <v>8552.4</v>
+        <v>2595.95</v>
       </c>
       <c r="E81" s="2">
-        <v>-1.36</v>
+        <v>0.01</v>
       </c>
       <c r="F81" s="2">
-        <v>-1.36</v>
+        <v>0.01</v>
       </c>
       <c r="G81" s="2">
-        <v>6.55</v>
+        <v>-1.6</v>
       </c>
       <c r="H81" s="2">
-        <v>-9.23</v>
+        <v>-0.61</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>8266.39</v>
+        <v>2632.11</v>
       </c>
       <c r="K81" s="1">
-        <v>8389.27</v>
+        <v>2605.09</v>
       </c>
       <c r="L81" s="1">
-        <v>8541.32</v>
+        <v>2646.22</v>
       </c>
       <c r="M81" s="3">
-        <v>-4.23</v>
+        <v>-14.47</v>
       </c>
       <c r="N81" s="3">
-        <v>-71.71</v>
+        <v>-13.4</v>
       </c>
       <c r="O81" s="3">
-        <v>68.86</v>
+        <v>-5.2</v>
       </c>
       <c r="P81" s="3">
-        <v>59.81</v>
+        <v>4.89</v>
       </c>
       <c r="Q81" s="3">
-        <v>375.34</v>
+        <v>89.61</v>
       </c>
       <c r="R81" s="3">
-        <v>514.31</v>
-      </c>
-      <c r="S81" t="str">
+        <v>106.33</v>
+      </c>
+      <c r="S81" s="3">
+        <v>26.38</v>
+      </c>
+      <c r="T81" s="3">
+        <v>15.33</v>
+      </c>
+      <c r="U81" s="3">
+        <v>38.25</v>
+      </c>
+      <c r="V81" s="3">
+        <v>38.87</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="str">
         <v/>
       </c>
     </row>
@@ -5189,57 +6647,75 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D82" s="1">
-        <v>3813</v>
+        <v>204.22</v>
       </c>
       <c r="E82" s="2">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
-        <v>0.81</v>
+        <v>3.78</v>
       </c>
       <c r="H82" s="2">
-        <v>-12.41</v>
+        <v>-18.03</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>4040.15</v>
+        <v>180.21</v>
       </c>
       <c r="K82" s="1">
-        <v>3803.95</v>
+        <v>201.48</v>
       </c>
       <c r="L82" s="1">
-        <v>3939.04</v>
+        <v>195.45</v>
       </c>
       <c r="M82" s="3">
-        <v>-36.3</v>
+        <v>2.88</v>
       </c>
       <c r="N82" s="3">
-        <v>-50.99</v>
+        <v>2.66</v>
       </c>
       <c r="O82" s="3">
-        <v>-64.32</v>
+        <v>12.32</v>
       </c>
       <c r="P82" s="3">
-        <v>-42.15</v>
+        <v>7.02</v>
       </c>
       <c r="Q82" s="3">
-        <v>127.86</v>
+        <v>5.47</v>
       </c>
       <c r="R82" s="3">
-        <v>207.1</v>
-      </c>
-      <c r="S82" t="str">
+        <v>7.68</v>
+      </c>
+      <c r="S82" s="3">
+        <v>100</v>
+      </c>
+      <c r="T82" s="3">
+        <v>99.62</v>
+      </c>
+      <c r="U82" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="V82" s="3">
+        <v>97.16</v>
+      </c>
+      <c r="W82" s="3">
+        <v>0</v>
+      </c>
+      <c r="X82" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="str">
         <v/>
       </c>
     </row>
@@ -5248,57 +6724,75 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D83" s="1">
-        <v>26836.5</v>
+        <v>1255.08</v>
       </c>
       <c r="E83" s="2">
-        <v>-1.38</v>
+        <v>-0.01</v>
       </c>
       <c r="F83" s="2">
-        <v>-1.38</v>
+        <v>-0.01</v>
       </c>
       <c r="G83" s="2">
-        <v>1.05</v>
+        <v>-1.42</v>
       </c>
       <c r="H83" s="2">
-        <v>-11.07</v>
+        <v>-0.51</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>28581.69</v>
+        <v>1268.29</v>
       </c>
       <c r="K83" s="1">
-        <v>26935.59</v>
+        <v>1262.72</v>
       </c>
       <c r="L83" s="1">
-        <v>27702.92</v>
+        <v>1278.74</v>
       </c>
       <c r="M83" s="3">
-        <v>-198.76</v>
+        <v>-5.99</v>
       </c>
       <c r="N83" s="3">
-        <v>-288.55</v>
+        <v>-4.77</v>
       </c>
       <c r="O83" s="3">
-        <v>-456.58</v>
+        <v>-0.92</v>
       </c>
       <c r="P83" s="3">
-        <v>-290.92</v>
+        <v>3.68</v>
       </c>
       <c r="Q83" s="3">
-        <v>1333.07</v>
+        <v>20.71</v>
       </c>
       <c r="R83" s="3">
-        <v>1904.53</v>
-      </c>
-      <c r="S83" t="str">
+        <v>21.83</v>
+      </c>
+      <c r="S83" s="3">
+        <v>15.42</v>
+      </c>
+      <c r="T83" s="3">
+        <v>15.68</v>
+      </c>
+      <c r="U83" s="3">
+        <v>81.87</v>
+      </c>
+      <c r="V83" s="3">
+        <v>44.07</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="str">
         <v/>
       </c>
     </row>
@@ -5307,57 +6801,75 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D84" s="1">
-        <v>43975.5</v>
+        <v>836.78</v>
       </c>
       <c r="E84" s="2">
-        <v>-1.44</v>
+        <v>-0.05</v>
       </c>
       <c r="F84" s="2">
-        <v>-1.44</v>
+        <v>-0.05</v>
       </c>
       <c r="G84" s="2">
-        <v>-1.2</v>
+        <v>-2.16</v>
       </c>
       <c r="H84" s="2">
-        <v>-20.73</v>
+        <v>-6.13</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>49087.83</v>
+        <v>873.29</v>
       </c>
       <c r="K84" s="1">
-        <v>44615.97</v>
+        <v>841.13</v>
       </c>
       <c r="L84" s="1">
-        <v>46121.99</v>
+        <v>859.84</v>
       </c>
       <c r="M84" s="3">
-        <v>-456.81</v>
+        <v>-6.58</v>
       </c>
       <c r="N84" s="3">
-        <v>-504.62</v>
+        <v>-6.2</v>
       </c>
       <c r="O84" s="3">
-        <v>-1598.77</v>
+        <v>-9.78</v>
       </c>
       <c r="P84" s="3">
-        <v>-1340.83</v>
+        <v>-6.48</v>
       </c>
       <c r="Q84" s="3">
-        <v>-2116.54</v>
+        <v>-17.32</v>
       </c>
       <c r="R84" s="3">
-        <v>-956.12</v>
-      </c>
-      <c r="S84" t="str">
+        <v>-14.22</v>
+      </c>
+      <c r="S84" s="3">
+        <v>20.1</v>
+      </c>
+      <c r="T84" s="3">
+        <v>9.82</v>
+      </c>
+      <c r="U84" s="3">
+        <v>42.87</v>
+      </c>
+      <c r="V84" s="3">
+        <v>53.9</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="str">
         <v/>
       </c>
     </row>
@@ -5366,57 +6878,75 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D85" s="1">
-        <v>24987.1</v>
+        <v>13591.6</v>
       </c>
       <c r="E85" s="2">
-        <v>-1.58</v>
+        <v>-0.07</v>
       </c>
       <c r="F85" s="2">
-        <v>-1.58</v>
+        <v>-0.07</v>
       </c>
       <c r="G85" s="2">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="H85" s="2">
-        <v>-9.51</v>
+        <v>-11.12</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>26250.15</v>
+        <v>14376.94</v>
       </c>
       <c r="K85" s="1">
-        <v>25067.99</v>
+        <v>13659.88</v>
       </c>
       <c r="L85" s="1">
-        <v>25597.84</v>
+        <v>13987.77</v>
       </c>
       <c r="M85" s="3">
-        <v>-121.71</v>
+        <v>-57.18</v>
       </c>
       <c r="N85" s="3">
-        <v>-206.59</v>
+        <v>-106.46</v>
       </c>
       <c r="O85" s="3">
-        <v>-331.83</v>
+        <v>-234.36</v>
       </c>
       <c r="P85" s="3">
-        <v>-217.64</v>
+        <v>-177.27</v>
       </c>
       <c r="Q85" s="3">
-        <v>674.52</v>
+        <v>-548.46</v>
       </c>
       <c r="R85" s="3">
-        <v>1086.46</v>
-      </c>
-      <c r="S85" t="str">
+        <v>-494.23</v>
+      </c>
+      <c r="S85" s="3">
+        <v>45.74</v>
+      </c>
+      <c r="T85" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="U85" s="3">
+        <v>26.87</v>
+      </c>
+      <c r="V85" s="3">
+        <v>25.08</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="str">
         <v/>
       </c>
     </row>
@@ -5425,57 +6955,75 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D86" s="1">
-        <v>27914.3</v>
+        <v>3280.86</v>
       </c>
       <c r="E86" s="2">
-        <v>-1.59</v>
+        <v>-0.1</v>
       </c>
       <c r="F86" s="2">
-        <v>-1.59</v>
+        <v>-0.1</v>
       </c>
       <c r="G86" s="2">
-        <v>-1.58</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
+        <v>-1.23</v>
+      </c>
+      <c r="H86" s="2">
+        <v>1.2</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
-      <c r="J86" t="str">
-        <v/>
+      <c r="J86" s="1">
+        <v>3295.53</v>
       </c>
       <c r="K86" s="1">
-        <v>28297.32</v>
+        <v>3292.04</v>
       </c>
       <c r="L86" s="1">
-        <v>29468.3</v>
+        <v>3345.3</v>
       </c>
       <c r="M86" s="3">
-        <v>-354.18</v>
+        <v>-17.47</v>
       </c>
       <c r="N86" s="3">
-        <v>-394.92</v>
+        <v>-17.28</v>
       </c>
       <c r="O86" s="3">
-        <v>-130.04</v>
+        <v>3.13</v>
       </c>
       <c r="P86" s="3">
-        <v>183.71</v>
+        <v>17.81</v>
       </c>
       <c r="Q86" s="3">
-        <v>282.81</v>
+        <v>136.08</v>
       </c>
       <c r="R86" s="3">
-        <v>197.84</v>
-      </c>
-      <c r="S86" t="str">
+        <v>153.82</v>
+      </c>
+      <c r="S86" s="3">
+        <v>30.89</v>
+      </c>
+      <c r="T86" s="3">
+        <v>8.22</v>
+      </c>
+      <c r="U86" s="3">
+        <v>35.85</v>
+      </c>
+      <c r="V86" s="3">
+        <v>51.02</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="str">
         <v/>
       </c>
     </row>
@@ -5484,57 +7032,75 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D87" s="1">
-        <v>25306.15</v>
+        <v>33851.1</v>
       </c>
       <c r="E87" s="2">
-        <v>-1.67</v>
+        <v>-0.21</v>
       </c>
       <c r="F87" s="2">
-        <v>-1.67</v>
+        <v>-0.21</v>
       </c>
       <c r="G87" s="2">
-        <v>-3.6</v>
+        <v>-7.58</v>
       </c>
       <c r="H87" s="2">
-        <v>12.24</v>
+        <v>-7.9</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>23595.54</v>
+        <v>37084.64</v>
       </c>
       <c r="K87" s="1">
-        <v>25736.65</v>
+        <v>35231.58</v>
       </c>
       <c r="L87" s="1">
-        <v>26179.41</v>
+        <v>38146.43</v>
       </c>
       <c r="M87" s="3">
-        <v>-172.58</v>
+        <v>-994.64</v>
       </c>
       <c r="N87" s="3">
-        <v>-106.49</v>
+        <v>-827.15</v>
       </c>
       <c r="O87" s="3">
-        <v>683.83</v>
+        <v>-536.15</v>
       </c>
       <c r="P87" s="3">
-        <v>871.75</v>
+        <v>129.18</v>
       </c>
       <c r="Q87" s="3">
-        <v>2363.37</v>
+        <v>527.27</v>
       </c>
       <c r="R87" s="3">
-        <v>2365.37</v>
-      </c>
-      <c r="S87" t="str">
+        <v>917.62</v>
+      </c>
+      <c r="S87" s="3">
+        <v>22.46</v>
+      </c>
+      <c r="T87" s="3">
+        <v>5.87</v>
+      </c>
+      <c r="U87" s="3">
+        <v>41.94</v>
+      </c>
+      <c r="V87" s="3">
+        <v>57.39</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="str">
         <v/>
       </c>
     </row>
@@ -5543,57 +7109,75 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D88" s="1">
-        <v>27189.1</v>
+        <v>1558.1</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.85</v>
+        <v>-0.34</v>
       </c>
       <c r="F88" s="2">
-        <v>-1.85</v>
+        <v>-0.34</v>
       </c>
       <c r="G88" s="2">
-        <v>1.85</v>
+        <v>-1.59</v>
       </c>
       <c r="H88" s="2">
-        <v>-5.33</v>
+        <v>7.85</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>27387.51</v>
+        <v>1470.05</v>
       </c>
       <c r="K88" s="1">
-        <v>27263.36</v>
+        <v>1592.78</v>
       </c>
       <c r="L88" s="1">
-        <v>27306.52</v>
+        <v>1573.92</v>
       </c>
       <c r="M88" s="3">
-        <v>29.87</v>
+        <v>8.97</v>
       </c>
       <c r="N88" s="3">
-        <v>-52.8</v>
+        <v>13.34</v>
       </c>
       <c r="O88" s="3">
-        <v>-11.17</v>
+        <v>28.19</v>
       </c>
       <c r="P88" s="3">
-        <v>23.26</v>
+        <v>30.68</v>
       </c>
       <c r="Q88" s="3">
-        <v>672.45</v>
+        <v>-75.38</v>
       </c>
       <c r="R88" s="3">
-        <v>880.38</v>
-      </c>
-      <c r="S88" t="str">
+        <v>-105.97</v>
+      </c>
+      <c r="S88" s="3">
+        <v>45.23</v>
+      </c>
+      <c r="T88" s="3">
+        <v>20.31</v>
+      </c>
+      <c r="U88" s="3">
+        <v>31.38</v>
+      </c>
+      <c r="V88" s="3">
+        <v>17.91</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="str">
         <v/>
       </c>
     </row>
@@ -5602,57 +7186,75 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D89" s="1">
-        <v>16229.05</v>
+        <v>235.15</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.27</v>
+        <v>-0.61</v>
       </c>
       <c r="F89" s="2">
-        <v>-2.27</v>
+        <v>-0.61</v>
       </c>
       <c r="G89" s="2">
-        <v>2</v>
+        <v>-0.34</v>
       </c>
       <c r="H89" s="2">
-        <v>-26.22</v>
+        <v>17.58</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>18456.36</v>
+        <v>219.44</v>
       </c>
       <c r="K89" s="1">
-        <v>16125.26</v>
+        <v>234.99</v>
       </c>
       <c r="L89" s="1">
-        <v>17256.4</v>
+        <v>228.28</v>
       </c>
       <c r="M89" s="3">
-        <v>-299.59</v>
+        <v>1.75</v>
       </c>
       <c r="N89" s="3">
-        <v>-425.54</v>
+        <v>2.27</v>
       </c>
       <c r="O89" s="3">
-        <v>-658.68</v>
+        <v>4.88</v>
       </c>
       <c r="P89" s="3">
-        <v>-508.53</v>
+        <v>3.75</v>
       </c>
       <c r="Q89" s="3">
-        <v>280.73</v>
+        <v>-0.69</v>
       </c>
       <c r="R89" s="3">
-        <v>929.94</v>
-      </c>
-      <c r="S89" t="str">
+        <v>-4.78</v>
+      </c>
+      <c r="S89" s="3">
+        <v>54.78</v>
+      </c>
+      <c r="T89" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="U89" s="3">
+        <v>11.31</v>
+      </c>
+      <c r="V89" s="3">
+        <v>42.89</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="str">
         <v/>
       </c>
     </row>
@@ -5661,63 +7263,81 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D90" s="1">
-        <v>10639.55</v>
+        <v>190.65</v>
       </c>
       <c r="E90" s="2">
-        <v>-2.27</v>
+        <v>-0.65</v>
       </c>
       <c r="F90" s="2">
-        <v>-2.27</v>
+        <v>-0.65</v>
       </c>
       <c r="G90" s="2">
-        <v>1.95</v>
+        <v>-0.39</v>
       </c>
       <c r="H90" s="2">
-        <v>-27.62</v>
+        <v>16.5</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>12233.4</v>
+        <v>178.82</v>
       </c>
       <c r="K90" s="1">
-        <v>10574.3</v>
+        <v>190.58</v>
       </c>
       <c r="L90" s="1">
-        <v>11321.07</v>
+        <v>185.18</v>
       </c>
       <c r="M90" s="3">
-        <v>-198.96</v>
+        <v>1.4</v>
       </c>
       <c r="N90" s="3">
-        <v>-281.64</v>
+        <v>1.82</v>
       </c>
       <c r="O90" s="3">
-        <v>-477.57</v>
+        <v>3.66</v>
       </c>
       <c r="P90" s="3">
-        <v>-383.86</v>
+        <v>2.72</v>
       </c>
       <c r="Q90" s="3">
-        <v>-3.9</v>
+        <v>-2.54</v>
       </c>
       <c r="R90" s="3">
-        <v>426.64</v>
-      </c>
-      <c r="S90" t="str">
+        <v>-6.04</v>
+      </c>
+      <c r="S90" s="3">
+        <v>54.52</v>
+      </c>
+      <c r="T90" s="3">
+        <v>26.26</v>
+      </c>
+      <c r="U90" s="3">
+        <v>11.45</v>
+      </c>
+      <c r="V90" s="3">
+        <v>42.42</v>
+      </c>
+      <c r="W90" s="3">
+        <v>0</v>
+      </c>
+      <c r="X90" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y90"/>
   </ignoredErrors>
 </worksheet>
 </file>